--- a/output/version3/test/20-10/MARL/IL/RL-RL (+comm+it)/(RL+RL) test results.xlsx
+++ b/output/version3/test/20-10/MARL/IL/RL-RL (+comm+it)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1124</v>
+        <v>870</v>
       </c>
       <c r="C2" t="n">
-        <v>947</v>
+        <v>977</v>
       </c>
       <c r="D2" t="n">
-        <v>1069</v>
+        <v>987</v>
       </c>
       <c r="E2" t="n">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="F2" t="n">
-        <v>901</v>
+        <v>970</v>
       </c>
       <c r="G2" t="n">
-        <v>978</v>
+        <v>931</v>
       </c>
       <c r="H2" t="n">
-        <v>1034</v>
+        <v>840</v>
       </c>
       <c r="I2" t="n">
-        <v>904</v>
+        <v>814</v>
       </c>
       <c r="J2" t="n">
-        <v>942</v>
+        <v>1019</v>
       </c>
       <c r="K2" t="n">
-        <v>1043</v>
+        <v>963</v>
       </c>
       <c r="L2" t="n">
-        <v>986.7</v>
+        <v>929.3</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>968</v>
+        <v>1012</v>
       </c>
       <c r="C3" t="n">
-        <v>920</v>
+        <v>1043</v>
       </c>
       <c r="D3" t="n">
-        <v>942</v>
+        <v>1022</v>
       </c>
       <c r="E3" t="n">
-        <v>882</v>
+        <v>993</v>
       </c>
       <c r="F3" t="n">
-        <v>886</v>
+        <v>874</v>
       </c>
       <c r="G3" t="n">
-        <v>1043</v>
+        <v>940</v>
       </c>
       <c r="H3" t="n">
-        <v>1077</v>
+        <v>979</v>
       </c>
       <c r="I3" t="n">
-        <v>876</v>
+        <v>909</v>
       </c>
       <c r="J3" t="n">
-        <v>825</v>
+        <v>1049</v>
       </c>
       <c r="K3" t="n">
-        <v>917</v>
+        <v>884</v>
       </c>
       <c r="L3" t="n">
-        <v>933.6</v>
+        <v>970.5</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
+        <v>934</v>
+      </c>
+      <c r="C4" t="n">
+        <v>831</v>
+      </c>
+      <c r="D4" t="n">
+        <v>989</v>
+      </c>
+      <c r="E4" t="n">
+        <v>900</v>
+      </c>
+      <c r="F4" t="n">
+        <v>854</v>
+      </c>
+      <c r="G4" t="n">
         <v>915</v>
       </c>
-      <c r="C4" t="n">
-        <v>1006</v>
-      </c>
-      <c r="D4" t="n">
-        <v>933</v>
-      </c>
-      <c r="E4" t="n">
-        <v>933</v>
-      </c>
-      <c r="F4" t="n">
-        <v>911</v>
-      </c>
-      <c r="G4" t="n">
-        <v>853</v>
-      </c>
       <c r="H4" t="n">
-        <v>826</v>
+        <v>815</v>
       </c>
       <c r="I4" t="n">
-        <v>880</v>
+        <v>908</v>
       </c>
       <c r="J4" t="n">
-        <v>915</v>
+        <v>788</v>
       </c>
       <c r="K4" t="n">
-        <v>909</v>
+        <v>833</v>
       </c>
       <c r="L4" t="n">
-        <v>908.1</v>
+        <v>876.7</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>829</v>
+        <v>897</v>
       </c>
       <c r="C5" t="n">
+        <v>812</v>
+      </c>
+      <c r="D5" t="n">
+        <v>854</v>
+      </c>
+      <c r="E5" t="n">
+        <v>984</v>
+      </c>
+      <c r="F5" t="n">
+        <v>840</v>
+      </c>
+      <c r="G5" t="n">
+        <v>944</v>
+      </c>
+      <c r="H5" t="n">
+        <v>897</v>
+      </c>
+      <c r="I5" t="n">
+        <v>956</v>
+      </c>
+      <c r="J5" t="n">
         <v>877</v>
       </c>
-      <c r="D5" t="n">
-        <v>802</v>
-      </c>
-      <c r="E5" t="n">
-        <v>856</v>
-      </c>
-      <c r="F5" t="n">
-        <v>951</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1011</v>
-      </c>
-      <c r="H5" t="n">
-        <v>955</v>
-      </c>
-      <c r="I5" t="n">
-        <v>824</v>
-      </c>
-      <c r="J5" t="n">
-        <v>885</v>
-      </c>
       <c r="K5" t="n">
-        <v>862</v>
+        <v>846</v>
       </c>
       <c r="L5" t="n">
-        <v>885.2</v>
+        <v>890.7</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>943</v>
+        <v>1014</v>
       </c>
       <c r="C6" t="n">
-        <v>938</v>
+        <v>1036</v>
       </c>
       <c r="D6" t="n">
-        <v>900</v>
+        <v>952</v>
       </c>
       <c r="E6" t="n">
-        <v>1179</v>
+        <v>936</v>
       </c>
       <c r="F6" t="n">
-        <v>905</v>
+        <v>821</v>
       </c>
       <c r="G6" t="n">
-        <v>914</v>
+        <v>854</v>
       </c>
       <c r="H6" t="n">
-        <v>994</v>
+        <v>868</v>
       </c>
       <c r="I6" t="n">
-        <v>984</v>
+        <v>830</v>
       </c>
       <c r="J6" t="n">
-        <v>849</v>
+        <v>1050</v>
       </c>
       <c r="K6" t="n">
-        <v>893</v>
+        <v>840</v>
       </c>
       <c r="L6" t="n">
-        <v>949.9</v>
+        <v>920.1</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>892</v>
+        <v>934</v>
       </c>
       <c r="C7" t="n">
-        <v>823</v>
+        <v>922</v>
       </c>
       <c r="D7" t="n">
-        <v>868</v>
+        <v>841</v>
       </c>
       <c r="E7" t="n">
-        <v>838</v>
+        <v>913</v>
       </c>
       <c r="F7" t="n">
-        <v>1048</v>
+        <v>835</v>
       </c>
       <c r="G7" t="n">
-        <v>1101</v>
+        <v>816</v>
       </c>
       <c r="H7" t="n">
-        <v>915</v>
+        <v>844</v>
       </c>
       <c r="I7" t="n">
-        <v>924</v>
+        <v>861</v>
       </c>
       <c r="J7" t="n">
-        <v>929</v>
+        <v>851</v>
       </c>
       <c r="K7" t="n">
-        <v>806</v>
+        <v>847</v>
       </c>
       <c r="L7" t="n">
-        <v>914.4</v>
+        <v>866.4</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>1022</v>
+        <v>962</v>
       </c>
       <c r="C8" t="n">
-        <v>948</v>
+        <v>1039</v>
       </c>
       <c r="D8" t="n">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="E8" t="n">
-        <v>937</v>
+        <v>885</v>
       </c>
       <c r="F8" t="n">
-        <v>922</v>
+        <v>891</v>
       </c>
       <c r="G8" t="n">
-        <v>968</v>
+        <v>923</v>
       </c>
       <c r="H8" t="n">
-        <v>923</v>
+        <v>961</v>
       </c>
       <c r="I8" t="n">
-        <v>911</v>
+        <v>951</v>
       </c>
       <c r="J8" t="n">
-        <v>933</v>
+        <v>918</v>
       </c>
       <c r="K8" t="n">
-        <v>940</v>
+        <v>976</v>
       </c>
       <c r="L8" t="n">
-        <v>945.6</v>
+        <v>946.4</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
+        <v>1022</v>
+      </c>
+      <c r="C9" t="n">
+        <v>948</v>
+      </c>
+      <c r="D9" t="n">
+        <v>871</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1002</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1114</v>
+      </c>
+      <c r="G9" t="n">
+        <v>858</v>
+      </c>
+      <c r="H9" t="n">
+        <v>981</v>
+      </c>
+      <c r="I9" t="n">
+        <v>915</v>
+      </c>
+      <c r="J9" t="n">
         <v>874</v>
       </c>
-      <c r="C9" t="n">
-        <v>783</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1006</v>
-      </c>
-      <c r="E9" t="n">
-        <v>909</v>
-      </c>
-      <c r="F9" t="n">
-        <v>942</v>
-      </c>
-      <c r="G9" t="n">
-        <v>890</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1031</v>
-      </c>
-      <c r="I9" t="n">
-        <v>982</v>
-      </c>
-      <c r="J9" t="n">
-        <v>902</v>
-      </c>
       <c r="K9" t="n">
-        <v>920</v>
+        <v>829</v>
       </c>
       <c r="L9" t="n">
-        <v>923.9</v>
+        <v>941.4</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="C10" t="n">
-        <v>833</v>
+        <v>976</v>
       </c>
       <c r="D10" t="n">
-        <v>783</v>
+        <v>889</v>
       </c>
       <c r="E10" t="n">
-        <v>917</v>
+        <v>973</v>
       </c>
       <c r="F10" t="n">
-        <v>876</v>
+        <v>821</v>
       </c>
       <c r="G10" t="n">
-        <v>810</v>
+        <v>839</v>
       </c>
       <c r="H10" t="n">
-        <v>814</v>
+        <v>916</v>
       </c>
       <c r="I10" t="n">
-        <v>1050</v>
+        <v>836</v>
       </c>
       <c r="J10" t="n">
-        <v>784</v>
+        <v>872</v>
       </c>
       <c r="K10" t="n">
-        <v>962</v>
+        <v>834</v>
       </c>
       <c r="L10" t="n">
-        <v>869.7</v>
+        <v>882.8</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>867</v>
+        <v>853</v>
       </c>
       <c r="C11" t="n">
-        <v>876</v>
+        <v>895</v>
       </c>
       <c r="D11" t="n">
-        <v>827</v>
+        <v>779</v>
       </c>
       <c r="E11" t="n">
-        <v>897</v>
+        <v>1060</v>
       </c>
       <c r="F11" t="n">
-        <v>857</v>
+        <v>978</v>
       </c>
       <c r="G11" t="n">
-        <v>785</v>
+        <v>888</v>
       </c>
       <c r="H11" t="n">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="I11" t="n">
-        <v>915</v>
+        <v>868</v>
       </c>
       <c r="J11" t="n">
-        <v>925</v>
+        <v>843</v>
       </c>
       <c r="K11" t="n">
-        <v>958</v>
+        <v>887</v>
       </c>
       <c r="L11" t="n">
-        <v>882.2</v>
+        <v>897.4</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>916</v>
+        <v>808</v>
       </c>
       <c r="C12" t="n">
-        <v>926</v>
+        <v>910</v>
       </c>
       <c r="D12" t="n">
-        <v>901</v>
+        <v>928</v>
       </c>
       <c r="E12" t="n">
-        <v>933</v>
+        <v>844</v>
       </c>
       <c r="F12" t="n">
-        <v>916</v>
+        <v>892</v>
       </c>
       <c r="G12" t="n">
-        <v>880</v>
+        <v>930</v>
       </c>
       <c r="H12" t="n">
-        <v>871</v>
+        <v>936</v>
       </c>
       <c r="I12" t="n">
-        <v>937</v>
+        <v>857</v>
       </c>
       <c r="J12" t="n">
-        <v>836</v>
+        <v>963</v>
       </c>
       <c r="K12" t="n">
-        <v>883</v>
+        <v>894</v>
       </c>
       <c r="L12" t="n">
-        <v>899.9</v>
+        <v>896.2</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>975</v>
+        <v>931</v>
       </c>
       <c r="C13" t="n">
-        <v>840</v>
+        <v>923</v>
       </c>
       <c r="D13" t="n">
-        <v>919</v>
+        <v>864</v>
       </c>
       <c r="E13" t="n">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="F13" t="n">
-        <v>846</v>
+        <v>818</v>
       </c>
       <c r="G13" t="n">
-        <v>926</v>
+        <v>982</v>
       </c>
       <c r="H13" t="n">
-        <v>831</v>
+        <v>790</v>
       </c>
       <c r="I13" t="n">
-        <v>826</v>
+        <v>951</v>
       </c>
       <c r="J13" t="n">
-        <v>823</v>
+        <v>923</v>
       </c>
       <c r="K13" t="n">
-        <v>983</v>
+        <v>827</v>
       </c>
       <c r="L13" t="n">
-        <v>889.7</v>
+        <v>894</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>894</v>
+        <v>901</v>
       </c>
       <c r="C14" t="n">
-        <v>883</v>
+        <v>985</v>
       </c>
       <c r="D14" t="n">
-        <v>909</v>
+        <v>1037</v>
       </c>
       <c r="E14" t="n">
-        <v>963</v>
+        <v>1149</v>
       </c>
       <c r="F14" t="n">
-        <v>994</v>
+        <v>1016</v>
       </c>
       <c r="G14" t="n">
-        <v>888</v>
+        <v>921</v>
       </c>
       <c r="H14" t="n">
-        <v>1002</v>
+        <v>1009</v>
       </c>
       <c r="I14" t="n">
-        <v>986</v>
+        <v>895</v>
       </c>
       <c r="J14" t="n">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="K14" t="n">
-        <v>1039</v>
+        <v>912</v>
       </c>
       <c r="L14" t="n">
-        <v>961.4</v>
+        <v>987.7</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>1071</v>
+        <v>1003</v>
       </c>
       <c r="C15" t="n">
-        <v>1003</v>
+        <v>962</v>
       </c>
       <c r="D15" t="n">
-        <v>945</v>
+        <v>858</v>
       </c>
       <c r="E15" t="n">
-        <v>1092</v>
+        <v>1014</v>
       </c>
       <c r="F15" t="n">
-        <v>1118</v>
+        <v>903</v>
       </c>
       <c r="G15" t="n">
-        <v>915</v>
+        <v>893</v>
       </c>
       <c r="H15" t="n">
-        <v>1065</v>
+        <v>907</v>
       </c>
       <c r="I15" t="n">
-        <v>991</v>
+        <v>908</v>
       </c>
       <c r="J15" t="n">
-        <v>1070</v>
+        <v>996</v>
       </c>
       <c r="K15" t="n">
-        <v>930</v>
+        <v>921</v>
       </c>
       <c r="L15" t="n">
-        <v>1020</v>
+        <v>936.5</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>1014</v>
+        <v>894</v>
       </c>
       <c r="C16" t="n">
-        <v>841</v>
+        <v>818</v>
       </c>
       <c r="D16" t="n">
-        <v>979</v>
+        <v>1026</v>
       </c>
       <c r="E16" t="n">
-        <v>894</v>
+        <v>830</v>
       </c>
       <c r="F16" t="n">
-        <v>882</v>
+        <v>949</v>
       </c>
       <c r="G16" t="n">
-        <v>908</v>
+        <v>852</v>
       </c>
       <c r="H16" t="n">
-        <v>899</v>
+        <v>844</v>
       </c>
       <c r="I16" t="n">
-        <v>898</v>
+        <v>917</v>
       </c>
       <c r="J16" t="n">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="K16" t="n">
-        <v>1035</v>
+        <v>939</v>
       </c>
       <c r="L16" t="n">
-        <v>921.9</v>
+        <v>894.9</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>933</v>
+        <v>879</v>
       </c>
       <c r="C17" t="n">
-        <v>818</v>
+        <v>853</v>
       </c>
       <c r="D17" t="n">
-        <v>719</v>
+        <v>764</v>
       </c>
       <c r="E17" t="n">
-        <v>760</v>
+        <v>747</v>
       </c>
       <c r="F17" t="n">
-        <v>779</v>
+        <v>1011</v>
       </c>
       <c r="G17" t="n">
-        <v>991</v>
+        <v>845</v>
       </c>
       <c r="H17" t="n">
-        <v>855</v>
+        <v>940</v>
       </c>
       <c r="I17" t="n">
-        <v>753</v>
+        <v>823</v>
       </c>
       <c r="J17" t="n">
-        <v>920</v>
+        <v>995</v>
       </c>
       <c r="K17" t="n">
-        <v>1087</v>
+        <v>755</v>
       </c>
       <c r="L17" t="n">
-        <v>861.5</v>
+        <v>861.2</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>1007</v>
+        <v>1043</v>
       </c>
       <c r="C18" t="n">
-        <v>1000</v>
+        <v>959</v>
       </c>
       <c r="D18" t="n">
-        <v>850</v>
+        <v>1065</v>
       </c>
       <c r="E18" t="n">
-        <v>1074</v>
+        <v>1124</v>
       </c>
       <c r="F18" t="n">
-        <v>1030</v>
+        <v>1081</v>
       </c>
       <c r="G18" t="n">
-        <v>1176</v>
+        <v>989</v>
       </c>
       <c r="H18" t="n">
-        <v>1019</v>
+        <v>870</v>
       </c>
       <c r="I18" t="n">
-        <v>988</v>
+        <v>1008</v>
       </c>
       <c r="J18" t="n">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="K18" t="n">
-        <v>1021</v>
+        <v>907</v>
       </c>
       <c r="L18" t="n">
-        <v>1004.9</v>
+        <v>992.4</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>786</v>
+        <v>755</v>
       </c>
       <c r="C19" t="n">
-        <v>806</v>
+        <v>794</v>
       </c>
       <c r="D19" t="n">
-        <v>833</v>
+        <v>808</v>
       </c>
       <c r="E19" t="n">
-        <v>798</v>
+        <v>781</v>
       </c>
       <c r="F19" t="n">
-        <v>794</v>
+        <v>865</v>
       </c>
       <c r="G19" t="n">
-        <v>920</v>
+        <v>814</v>
       </c>
       <c r="H19" t="n">
-        <v>836</v>
+        <v>864</v>
       </c>
       <c r="I19" t="n">
-        <v>728</v>
+        <v>955</v>
       </c>
       <c r="J19" t="n">
-        <v>709</v>
+        <v>904</v>
       </c>
       <c r="K19" t="n">
-        <v>721</v>
+        <v>958</v>
       </c>
       <c r="L19" t="n">
-        <v>793.1</v>
+        <v>849.8</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>771</v>
+        <v>844</v>
       </c>
       <c r="C20" t="n">
-        <v>950</v>
+        <v>748</v>
       </c>
       <c r="D20" t="n">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="E20" t="n">
-        <v>834</v>
+        <v>849</v>
       </c>
       <c r="F20" t="n">
-        <v>864</v>
+        <v>839</v>
       </c>
       <c r="G20" t="n">
-        <v>923</v>
+        <v>748</v>
       </c>
       <c r="H20" t="n">
-        <v>853</v>
+        <v>928</v>
       </c>
       <c r="I20" t="n">
-        <v>823</v>
+        <v>947</v>
       </c>
       <c r="J20" t="n">
-        <v>992</v>
+        <v>795</v>
       </c>
       <c r="K20" t="n">
-        <v>774</v>
+        <v>905</v>
       </c>
       <c r="L20" t="n">
-        <v>861.1</v>
+        <v>843.3</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>945</v>
+        <v>837</v>
       </c>
       <c r="C21" t="n">
-        <v>863</v>
+        <v>1000</v>
       </c>
       <c r="D21" t="n">
-        <v>944</v>
+        <v>1021</v>
       </c>
       <c r="E21" t="n">
-        <v>1073</v>
+        <v>1005</v>
       </c>
       <c r="F21" t="n">
-        <v>996</v>
+        <v>959</v>
       </c>
       <c r="G21" t="n">
-        <v>913</v>
+        <v>961</v>
       </c>
       <c r="H21" t="n">
-        <v>995</v>
+        <v>1040</v>
       </c>
       <c r="I21" t="n">
-        <v>900</v>
+        <v>915</v>
       </c>
       <c r="J21" t="n">
-        <v>985</v>
+        <v>925</v>
       </c>
       <c r="K21" t="n">
-        <v>938</v>
+        <v>905</v>
       </c>
       <c r="L21" t="n">
-        <v>955.2</v>
+        <v>956.8</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>810</v>
+        <v>866</v>
       </c>
       <c r="C22" t="n">
-        <v>900</v>
+        <v>1013</v>
       </c>
       <c r="D22" t="n">
-        <v>855</v>
+        <v>872</v>
       </c>
       <c r="E22" t="n">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="F22" t="n">
-        <v>893</v>
+        <v>1070</v>
       </c>
       <c r="G22" t="n">
-        <v>814</v>
+        <v>837</v>
       </c>
       <c r="H22" t="n">
-        <v>825</v>
+        <v>847</v>
       </c>
       <c r="I22" t="n">
-        <v>824</v>
+        <v>878</v>
       </c>
       <c r="J22" t="n">
-        <v>869</v>
+        <v>986</v>
       </c>
       <c r="K22" t="n">
-        <v>885</v>
+        <v>799</v>
       </c>
       <c r="L22" t="n">
-        <v>856.7</v>
+        <v>905.5</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>820</v>
+        <v>1048</v>
       </c>
       <c r="C23" t="n">
-        <v>946</v>
+        <v>951</v>
       </c>
       <c r="D23" t="n">
-        <v>837</v>
+        <v>779</v>
       </c>
       <c r="E23" t="n">
-        <v>1031</v>
+        <v>870</v>
       </c>
       <c r="F23" t="n">
-        <v>1028</v>
+        <v>918</v>
       </c>
       <c r="G23" t="n">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="H23" t="n">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="I23" t="n">
-        <v>947</v>
+        <v>984</v>
       </c>
       <c r="J23" t="n">
-        <v>945</v>
+        <v>918</v>
       </c>
       <c r="K23" t="n">
-        <v>911</v>
+        <v>954</v>
       </c>
       <c r="L23" t="n">
-        <v>921.5</v>
+        <v>917.3</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>879</v>
+        <v>810</v>
       </c>
       <c r="C24" t="n">
-        <v>884</v>
+        <v>918</v>
       </c>
       <c r="D24" t="n">
-        <v>1014</v>
+        <v>856</v>
       </c>
       <c r="E24" t="n">
-        <v>929</v>
+        <v>957</v>
       </c>
       <c r="F24" t="n">
-        <v>986</v>
+        <v>837</v>
       </c>
       <c r="G24" t="n">
-        <v>835</v>
+        <v>1010</v>
       </c>
       <c r="H24" t="n">
-        <v>889</v>
+        <v>963</v>
       </c>
       <c r="I24" t="n">
-        <v>749</v>
+        <v>919</v>
       </c>
       <c r="J24" t="n">
-        <v>906</v>
+        <v>874</v>
       </c>
       <c r="K24" t="n">
-        <v>997</v>
+        <v>872</v>
       </c>
       <c r="L24" t="n">
-        <v>906.8</v>
+        <v>901.6</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>942</v>
+        <v>924</v>
       </c>
       <c r="C25" t="n">
-        <v>1006</v>
+        <v>868</v>
       </c>
       <c r="D25" t="n">
-        <v>847</v>
+        <v>987</v>
       </c>
       <c r="E25" t="n">
-        <v>929</v>
+        <v>938</v>
       </c>
       <c r="F25" t="n">
-        <v>1018</v>
+        <v>839</v>
       </c>
       <c r="G25" t="n">
-        <v>1044</v>
+        <v>1052</v>
       </c>
       <c r="H25" t="n">
-        <v>909</v>
+        <v>864</v>
       </c>
       <c r="I25" t="n">
-        <v>1068</v>
+        <v>1050</v>
       </c>
       <c r="J25" t="n">
-        <v>936</v>
+        <v>1060</v>
       </c>
       <c r="K25" t="n">
-        <v>996</v>
+        <v>836</v>
       </c>
       <c r="L25" t="n">
-        <v>969.5</v>
+        <v>941.8</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>906</v>
+        <v>1032</v>
       </c>
       <c r="C26" t="n">
-        <v>955</v>
+        <v>1023</v>
       </c>
       <c r="D26" t="n">
-        <v>992</v>
+        <v>1063</v>
       </c>
       <c r="E26" t="n">
-        <v>947</v>
+        <v>900</v>
       </c>
       <c r="F26" t="n">
-        <v>993</v>
+        <v>926</v>
       </c>
       <c r="G26" t="n">
-        <v>955</v>
+        <v>984</v>
       </c>
       <c r="H26" t="n">
-        <v>1042</v>
+        <v>1017</v>
       </c>
       <c r="I26" t="n">
-        <v>996</v>
+        <v>1101</v>
       </c>
       <c r="J26" t="n">
         <v>941</v>
       </c>
       <c r="K26" t="n">
-        <v>898</v>
+        <v>1036</v>
       </c>
       <c r="L26" t="n">
-        <v>962.5</v>
+        <v>1002.3</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>906</v>
+        <v>921</v>
       </c>
       <c r="C27" t="n">
-        <v>1079</v>
+        <v>985</v>
       </c>
       <c r="D27" t="n">
-        <v>964</v>
+        <v>893</v>
       </c>
       <c r="E27" t="n">
-        <v>1182</v>
+        <v>872</v>
       </c>
       <c r="F27" t="n">
-        <v>923</v>
+        <v>946</v>
       </c>
       <c r="G27" t="n">
-        <v>901</v>
+        <v>910</v>
       </c>
       <c r="H27" t="n">
-        <v>900</v>
+        <v>930</v>
       </c>
       <c r="I27" t="n">
-        <v>976</v>
+        <v>1059</v>
       </c>
       <c r="J27" t="n">
-        <v>1032</v>
+        <v>907</v>
       </c>
       <c r="K27" t="n">
-        <v>961</v>
+        <v>917</v>
       </c>
       <c r="L27" t="n">
-        <v>982.4</v>
+        <v>934</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>866</v>
+        <v>953</v>
       </c>
       <c r="C28" t="n">
-        <v>876</v>
+        <v>831</v>
       </c>
       <c r="D28" t="n">
-        <v>912</v>
+        <v>826</v>
       </c>
       <c r="E28" t="n">
-        <v>962</v>
+        <v>742</v>
       </c>
       <c r="F28" t="n">
-        <v>989</v>
+        <v>885</v>
       </c>
       <c r="G28" t="n">
-        <v>868</v>
+        <v>1030</v>
       </c>
       <c r="H28" t="n">
-        <v>746</v>
+        <v>825</v>
       </c>
       <c r="I28" t="n">
-        <v>860</v>
+        <v>873</v>
       </c>
       <c r="J28" t="n">
-        <v>821</v>
+        <v>858</v>
       </c>
       <c r="K28" t="n">
-        <v>845</v>
+        <v>813</v>
       </c>
       <c r="L28" t="n">
-        <v>874.5</v>
+        <v>863.6</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="C29" t="n">
-        <v>856</v>
+        <v>881</v>
       </c>
       <c r="D29" t="n">
-        <v>923</v>
+        <v>912</v>
       </c>
       <c r="E29" t="n">
-        <v>934</v>
+        <v>861</v>
       </c>
       <c r="F29" t="n">
-        <v>921</v>
+        <v>881</v>
       </c>
       <c r="G29" t="n">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="H29" t="n">
-        <v>889</v>
+        <v>862</v>
       </c>
       <c r="I29" t="n">
-        <v>901</v>
+        <v>861</v>
       </c>
       <c r="J29" t="n">
-        <v>866</v>
+        <v>894</v>
       </c>
       <c r="K29" t="n">
-        <v>905</v>
+        <v>926</v>
       </c>
       <c r="L29" t="n">
-        <v>892</v>
+        <v>881.8</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="C30" t="n">
-        <v>780</v>
+        <v>1005</v>
       </c>
       <c r="D30" t="n">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="E30" t="n">
-        <v>903</v>
+        <v>759</v>
       </c>
       <c r="F30" t="n">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="G30" t="n">
-        <v>919</v>
+        <v>810</v>
       </c>
       <c r="H30" t="n">
-        <v>842</v>
+        <v>860</v>
       </c>
       <c r="I30" t="n">
-        <v>913</v>
+        <v>821</v>
       </c>
       <c r="J30" t="n">
-        <v>933</v>
+        <v>846</v>
       </c>
       <c r="K30" t="n">
-        <v>936</v>
+        <v>789</v>
       </c>
       <c r="L30" t="n">
-        <v>894.7</v>
+        <v>861.8</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>1081</v>
+        <v>982</v>
       </c>
       <c r="C31" t="n">
-        <v>1110</v>
+        <v>904</v>
       </c>
       <c r="D31" t="n">
-        <v>815</v>
+        <v>996</v>
       </c>
       <c r="E31" t="n">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="F31" t="n">
-        <v>1016</v>
+        <v>915</v>
       </c>
       <c r="G31" t="n">
-        <v>1035</v>
+        <v>882</v>
       </c>
       <c r="H31" t="n">
-        <v>889</v>
+        <v>944</v>
       </c>
       <c r="I31" t="n">
-        <v>1086</v>
+        <v>1056</v>
       </c>
       <c r="J31" t="n">
-        <v>994</v>
+        <v>877</v>
       </c>
       <c r="K31" t="n">
-        <v>924</v>
+        <v>1112</v>
       </c>
       <c r="L31" t="n">
-        <v>994.2</v>
+        <v>965.4</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>1067</v>
+        <v>986</v>
       </c>
       <c r="C32" t="n">
-        <v>942</v>
+        <v>1009</v>
       </c>
       <c r="D32" t="n">
-        <v>1178</v>
+        <v>1142</v>
       </c>
       <c r="E32" t="n">
-        <v>1053</v>
+        <v>969</v>
       </c>
       <c r="F32" t="n">
-        <v>1069</v>
+        <v>1145</v>
       </c>
       <c r="G32" t="n">
-        <v>953</v>
+        <v>1059</v>
       </c>
       <c r="H32" t="n">
-        <v>997</v>
+        <v>1004</v>
       </c>
       <c r="I32" t="n">
-        <v>993</v>
+        <v>1017</v>
       </c>
       <c r="J32" t="n">
-        <v>1151</v>
+        <v>1052</v>
       </c>
       <c r="K32" t="n">
-        <v>1231</v>
+        <v>1066</v>
       </c>
       <c r="L32" t="n">
-        <v>1063.4</v>
+        <v>1044.9</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>973</v>
+        <v>1129</v>
       </c>
       <c r="C33" t="n">
-        <v>923</v>
+        <v>905</v>
       </c>
       <c r="D33" t="n">
-        <v>795</v>
+        <v>903</v>
       </c>
       <c r="E33" t="n">
-        <v>887</v>
+        <v>905</v>
       </c>
       <c r="F33" t="n">
-        <v>884</v>
+        <v>857</v>
       </c>
       <c r="G33" t="n">
-        <v>955</v>
+        <v>979</v>
       </c>
       <c r="H33" t="n">
-        <v>953</v>
+        <v>902</v>
       </c>
       <c r="I33" t="n">
-        <v>927</v>
+        <v>897</v>
       </c>
       <c r="J33" t="n">
-        <v>825</v>
+        <v>835</v>
       </c>
       <c r="K33" t="n">
-        <v>866</v>
+        <v>1071</v>
       </c>
       <c r="L33" t="n">
-        <v>898.8</v>
+        <v>938.3</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>914</v>
+        <v>939</v>
       </c>
       <c r="C34" t="n">
-        <v>841</v>
+        <v>915</v>
       </c>
       <c r="D34" t="n">
-        <v>917</v>
+        <v>1036</v>
       </c>
       <c r="E34" t="n">
-        <v>887</v>
+        <v>1059</v>
       </c>
       <c r="F34" t="n">
-        <v>988</v>
+        <v>1015</v>
       </c>
       <c r="G34" t="n">
-        <v>951</v>
+        <v>1027</v>
       </c>
       <c r="H34" t="n">
-        <v>820</v>
+        <v>977</v>
       </c>
       <c r="I34" t="n">
-        <v>1005</v>
+        <v>837</v>
       </c>
       <c r="J34" t="n">
-        <v>1031</v>
+        <v>976</v>
       </c>
       <c r="K34" t="n">
-        <v>1041</v>
+        <v>1064</v>
       </c>
       <c r="L34" t="n">
-        <v>939.5</v>
+        <v>984.5</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>1029</v>
+        <v>1047</v>
       </c>
       <c r="C35" t="n">
-        <v>996</v>
+        <v>918</v>
       </c>
       <c r="D35" t="n">
-        <v>899</v>
+        <v>1021</v>
       </c>
       <c r="E35" t="n">
-        <v>986</v>
+        <v>961</v>
       </c>
       <c r="F35" t="n">
-        <v>1056</v>
+        <v>886</v>
       </c>
       <c r="G35" t="n">
-        <v>946</v>
+        <v>923</v>
       </c>
       <c r="H35" t="n">
-        <v>931</v>
+        <v>1011</v>
       </c>
       <c r="I35" t="n">
-        <v>1010</v>
+        <v>971</v>
       </c>
       <c r="J35" t="n">
-        <v>918</v>
+        <v>904</v>
       </c>
       <c r="K35" t="n">
-        <v>982</v>
+        <v>1028</v>
       </c>
       <c r="L35" t="n">
-        <v>975.3</v>
+        <v>967</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>882</v>
+        <v>922</v>
       </c>
       <c r="C36" t="n">
-        <v>997</v>
+        <v>942</v>
       </c>
       <c r="D36" t="n">
-        <v>900</v>
+        <v>919</v>
       </c>
       <c r="E36" t="n">
-        <v>944</v>
+        <v>918</v>
       </c>
       <c r="F36" t="n">
-        <v>926</v>
+        <v>893</v>
       </c>
       <c r="G36" t="n">
-        <v>986</v>
+        <v>831</v>
       </c>
       <c r="H36" t="n">
-        <v>988</v>
+        <v>898</v>
       </c>
       <c r="I36" t="n">
-        <v>934</v>
+        <v>877</v>
       </c>
       <c r="J36" t="n">
+        <v>922</v>
+      </c>
+      <c r="K36" t="n">
         <v>933</v>
       </c>
-      <c r="K36" t="n">
-        <v>864</v>
-      </c>
       <c r="L36" t="n">
-        <v>935.4</v>
+        <v>905.5</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>916</v>
+        <v>975</v>
       </c>
       <c r="C37" t="n">
-        <v>968</v>
+        <v>940</v>
       </c>
       <c r="D37" t="n">
-        <v>931</v>
+        <v>882</v>
       </c>
       <c r="E37" t="n">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="F37" t="n">
-        <v>855</v>
+        <v>884</v>
       </c>
       <c r="G37" t="n">
-        <v>905</v>
+        <v>947</v>
       </c>
       <c r="H37" t="n">
-        <v>993</v>
+        <v>889</v>
       </c>
       <c r="I37" t="n">
-        <v>963</v>
+        <v>882</v>
       </c>
       <c r="J37" t="n">
-        <v>896</v>
+        <v>979</v>
       </c>
       <c r="K37" t="n">
-        <v>850</v>
+        <v>1013</v>
       </c>
       <c r="L37" t="n">
-        <v>914.6</v>
+        <v>925.7</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>785</v>
+        <v>814</v>
       </c>
       <c r="C38" t="n">
-        <v>805</v>
+        <v>908</v>
       </c>
       <c r="D38" t="n">
-        <v>797</v>
+        <v>893</v>
       </c>
       <c r="E38" t="n">
-        <v>855</v>
+        <v>899</v>
       </c>
       <c r="F38" t="n">
-        <v>823</v>
+        <v>923</v>
       </c>
       <c r="G38" t="n">
-        <v>838</v>
+        <v>793</v>
       </c>
       <c r="H38" t="n">
-        <v>911</v>
+        <v>900</v>
       </c>
       <c r="I38" t="n">
-        <v>954</v>
+        <v>811</v>
       </c>
       <c r="J38" t="n">
-        <v>869</v>
+        <v>947</v>
       </c>
       <c r="K38" t="n">
-        <v>830</v>
+        <v>897</v>
       </c>
       <c r="L38" t="n">
-        <v>846.7</v>
+        <v>878.5</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>897</v>
+        <v>944</v>
       </c>
       <c r="C39" t="n">
-        <v>898</v>
+        <v>933</v>
       </c>
       <c r="D39" t="n">
-        <v>847</v>
+        <v>972</v>
       </c>
       <c r="E39" t="n">
-        <v>947</v>
+        <v>819</v>
       </c>
       <c r="F39" t="n">
-        <v>935</v>
+        <v>913</v>
       </c>
       <c r="G39" t="n">
-        <v>831</v>
+        <v>941</v>
       </c>
       <c r="H39" t="n">
-        <v>1073</v>
+        <v>894</v>
       </c>
       <c r="I39" t="n">
-        <v>994</v>
+        <v>889</v>
       </c>
       <c r="J39" t="n">
-        <v>868</v>
+        <v>969</v>
       </c>
       <c r="K39" t="n">
-        <v>886</v>
+        <v>979</v>
       </c>
       <c r="L39" t="n">
-        <v>917.6</v>
+        <v>925.3</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>899</v>
+        <v>843</v>
       </c>
       <c r="C40" t="n">
-        <v>851</v>
+        <v>920</v>
       </c>
       <c r="D40" t="n">
-        <v>984</v>
+        <v>848</v>
       </c>
       <c r="E40" t="n">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="F40" t="n">
-        <v>848</v>
+        <v>836</v>
       </c>
       <c r="G40" t="n">
-        <v>845</v>
+        <v>981</v>
       </c>
       <c r="H40" t="n">
-        <v>796</v>
+        <v>824</v>
       </c>
       <c r="I40" t="n">
-        <v>826</v>
+        <v>807</v>
       </c>
       <c r="J40" t="n">
-        <v>866</v>
+        <v>885</v>
       </c>
       <c r="K40" t="n">
-        <v>781</v>
+        <v>813</v>
       </c>
       <c r="L40" t="n">
-        <v>849.6</v>
+        <v>856</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>761</v>
+        <v>726</v>
       </c>
       <c r="C41" t="n">
-        <v>826</v>
+        <v>892</v>
       </c>
       <c r="D41" t="n">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="E41" t="n">
-        <v>753</v>
+        <v>763</v>
       </c>
       <c r="F41" t="n">
-        <v>790</v>
+        <v>900</v>
       </c>
       <c r="G41" t="n">
-        <v>882</v>
+        <v>816</v>
       </c>
       <c r="H41" t="n">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="I41" t="n">
-        <v>857</v>
+        <v>930</v>
       </c>
       <c r="J41" t="n">
-        <v>807</v>
+        <v>901</v>
       </c>
       <c r="K41" t="n">
-        <v>814</v>
+        <v>901</v>
       </c>
       <c r="L41" t="n">
-        <v>811.6</v>
+        <v>845.4</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>852</v>
+        <v>954</v>
       </c>
       <c r="C42" t="n">
-        <v>733</v>
+        <v>866</v>
       </c>
       <c r="D42" t="n">
-        <v>957</v>
+        <v>753</v>
       </c>
       <c r="E42" t="n">
-        <v>741</v>
+        <v>919</v>
       </c>
       <c r="F42" t="n">
-        <v>864</v>
+        <v>759</v>
       </c>
       <c r="G42" t="n">
-        <v>876</v>
+        <v>950</v>
       </c>
       <c r="H42" t="n">
-        <v>752</v>
+        <v>845</v>
       </c>
       <c r="I42" t="n">
-        <v>799</v>
+        <v>924</v>
       </c>
       <c r="J42" t="n">
-        <v>760</v>
+        <v>837</v>
       </c>
       <c r="K42" t="n">
-        <v>816</v>
+        <v>860</v>
       </c>
       <c r="L42" t="n">
-        <v>815</v>
+        <v>866.7</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>871</v>
+        <v>823</v>
       </c>
       <c r="C43" t="n">
-        <v>828</v>
+        <v>1020</v>
       </c>
       <c r="D43" t="n">
-        <v>980</v>
+        <v>902</v>
       </c>
       <c r="E43" t="n">
-        <v>929</v>
+        <v>889</v>
       </c>
       <c r="F43" t="n">
-        <v>921</v>
+        <v>906</v>
       </c>
       <c r="G43" t="n">
-        <v>940</v>
+        <v>751</v>
       </c>
       <c r="H43" t="n">
-        <v>866</v>
+        <v>844</v>
       </c>
       <c r="I43" t="n">
-        <v>893</v>
+        <v>974</v>
       </c>
       <c r="J43" t="n">
-        <v>905</v>
+        <v>881</v>
       </c>
       <c r="K43" t="n">
-        <v>899</v>
+        <v>787</v>
       </c>
       <c r="L43" t="n">
-        <v>903.2</v>
+        <v>877.7</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>766</v>
+        <v>833</v>
       </c>
       <c r="C44" t="n">
-        <v>844</v>
+        <v>822</v>
       </c>
       <c r="D44" t="n">
-        <v>929</v>
+        <v>778</v>
       </c>
       <c r="E44" t="n">
-        <v>724</v>
+        <v>1038</v>
       </c>
       <c r="F44" t="n">
-        <v>824</v>
+        <v>892</v>
       </c>
       <c r="G44" t="n">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="H44" t="n">
-        <v>794</v>
+        <v>706</v>
       </c>
       <c r="I44" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="J44" t="n">
-        <v>802</v>
+        <v>867</v>
       </c>
       <c r="K44" t="n">
-        <v>852</v>
+        <v>876</v>
       </c>
       <c r="L44" t="n">
-        <v>812.9</v>
+        <v>839.5</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>943</v>
+        <v>1118</v>
       </c>
       <c r="C45" t="n">
-        <v>977</v>
+        <v>951</v>
       </c>
       <c r="D45" t="n">
-        <v>1107</v>
+        <v>1127</v>
       </c>
       <c r="E45" t="n">
-        <v>1131</v>
+        <v>1150</v>
       </c>
       <c r="F45" t="n">
-        <v>1090</v>
+        <v>965</v>
       </c>
       <c r="G45" t="n">
-        <v>1092</v>
+        <v>1141</v>
       </c>
       <c r="H45" t="n">
-        <v>992</v>
+        <v>1057</v>
       </c>
       <c r="I45" t="n">
-        <v>984</v>
+        <v>1063</v>
       </c>
       <c r="J45" t="n">
-        <v>974</v>
+        <v>1083</v>
       </c>
       <c r="K45" t="n">
-        <v>1166</v>
+        <v>1028</v>
       </c>
       <c r="L45" t="n">
-        <v>1045.6</v>
+        <v>1068.3</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>886</v>
+        <v>944</v>
       </c>
       <c r="C46" t="n">
-        <v>933</v>
+        <v>976</v>
       </c>
       <c r="D46" t="n">
-        <v>889</v>
+        <v>774</v>
       </c>
       <c r="E46" t="n">
-        <v>955</v>
+        <v>829</v>
       </c>
       <c r="F46" t="n">
-        <v>824</v>
+        <v>944</v>
       </c>
       <c r="G46" t="n">
-        <v>828</v>
+        <v>1027</v>
       </c>
       <c r="H46" t="n">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="I46" t="n">
-        <v>971</v>
+        <v>988</v>
       </c>
       <c r="J46" t="n">
-        <v>857</v>
+        <v>833</v>
       </c>
       <c r="K46" t="n">
-        <v>886</v>
+        <v>1005</v>
       </c>
       <c r="L46" t="n">
-        <v>890.3</v>
+        <v>919.1</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>1003</v>
+        <v>992</v>
       </c>
       <c r="C47" t="n">
-        <v>934</v>
+        <v>1045</v>
       </c>
       <c r="D47" t="n">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="E47" t="n">
-        <v>1028</v>
+        <v>1007</v>
       </c>
       <c r="F47" t="n">
-        <v>1040</v>
+        <v>910</v>
       </c>
       <c r="G47" t="n">
-        <v>909</v>
+        <v>1050</v>
       </c>
       <c r="H47" t="n">
-        <v>1062</v>
+        <v>902</v>
       </c>
       <c r="I47" t="n">
-        <v>932</v>
+        <v>860</v>
       </c>
       <c r="J47" t="n">
-        <v>905</v>
+        <v>880</v>
       </c>
       <c r="K47" t="n">
-        <v>1103</v>
+        <v>981</v>
       </c>
       <c r="L47" t="n">
-        <v>993.1</v>
+        <v>963.6</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>763</v>
+        <v>863</v>
       </c>
       <c r="C48" t="n">
-        <v>799</v>
+        <v>818</v>
       </c>
       <c r="D48" t="n">
-        <v>836</v>
+        <v>751</v>
       </c>
       <c r="E48" t="n">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="F48" t="n">
-        <v>742</v>
+        <v>934</v>
       </c>
       <c r="G48" t="n">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="H48" t="n">
-        <v>786</v>
+        <v>679</v>
       </c>
       <c r="I48" t="n">
-        <v>757</v>
+        <v>850</v>
       </c>
       <c r="J48" t="n">
-        <v>786</v>
+        <v>821</v>
       </c>
       <c r="K48" t="n">
-        <v>679</v>
+        <v>785</v>
       </c>
       <c r="L48" t="n">
-        <v>779.4</v>
+        <v>814.4</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>1028</v>
+        <v>980</v>
       </c>
       <c r="C49" t="n">
-        <v>951</v>
+        <v>898</v>
       </c>
       <c r="D49" t="n">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="E49" t="n">
-        <v>843</v>
+        <v>831</v>
       </c>
       <c r="F49" t="n">
-        <v>806</v>
+        <v>950</v>
       </c>
       <c r="G49" t="n">
-        <v>951</v>
+        <v>868</v>
       </c>
       <c r="H49" t="n">
-        <v>942</v>
+        <v>848</v>
       </c>
       <c r="I49" t="n">
-        <v>817</v>
+        <v>874</v>
       </c>
       <c r="J49" t="n">
-        <v>843</v>
+        <v>802</v>
       </c>
       <c r="K49" t="n">
         <v>927</v>
       </c>
       <c r="L49" t="n">
-        <v>903.6</v>
+        <v>890.1</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>889</v>
+        <v>861</v>
       </c>
       <c r="C50" t="n">
-        <v>792</v>
+        <v>831</v>
       </c>
       <c r="D50" t="n">
-        <v>949</v>
+        <v>994</v>
       </c>
       <c r="E50" t="n">
-        <v>816</v>
+        <v>897</v>
       </c>
       <c r="F50" t="n">
-        <v>824</v>
+        <v>993</v>
       </c>
       <c r="G50" t="n">
-        <v>887</v>
+        <v>859</v>
       </c>
       <c r="H50" t="n">
-        <v>835</v>
+        <v>937</v>
       </c>
       <c r="I50" t="n">
-        <v>970</v>
+        <v>834</v>
       </c>
       <c r="J50" t="n">
-        <v>847</v>
+        <v>925</v>
       </c>
       <c r="K50" t="n">
-        <v>930</v>
+        <v>884</v>
       </c>
       <c r="L50" t="n">
-        <v>873.9</v>
+        <v>901.5</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>888</v>
+        <v>935</v>
       </c>
       <c r="C51" t="n">
-        <v>943</v>
+        <v>924</v>
       </c>
       <c r="D51" t="n">
-        <v>1043</v>
+        <v>937</v>
       </c>
       <c r="E51" t="n">
-        <v>1001</v>
+        <v>922</v>
       </c>
       <c r="F51" t="n">
-        <v>1006</v>
+        <v>954</v>
       </c>
       <c r="G51" t="n">
-        <v>787</v>
+        <v>863</v>
       </c>
       <c r="H51" t="n">
-        <v>886</v>
+        <v>996</v>
       </c>
       <c r="I51" t="n">
-        <v>956</v>
+        <v>981</v>
       </c>
       <c r="J51" t="n">
-        <v>898</v>
+        <v>922</v>
       </c>
       <c r="K51" t="n">
-        <v>903</v>
+        <v>958</v>
       </c>
       <c r="L51" t="n">
-        <v>931.1</v>
+        <v>939.2</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
+        <v>926.1799999999999</v>
+      </c>
+      <c r="C52" t="n">
+        <v>924.86</v>
+      </c>
+      <c r="D52" t="n">
+        <v>914.9</v>
+      </c>
+      <c r="E52" t="n">
+        <v>918</v>
+      </c>
+      <c r="F52" t="n">
+        <v>918.92</v>
+      </c>
+      <c r="G52" t="n">
+        <v>908.84</v>
+      </c>
+      <c r="H52" t="n">
+        <v>898.3</v>
+      </c>
+      <c r="I52" t="n">
         <v>914.04</v>
       </c>
-      <c r="C52" t="n">
-        <v>901.08</v>
-      </c>
-      <c r="D52" t="n">
-        <v>912.08</v>
-      </c>
-      <c r="E52" t="n">
-        <v>926.3</v>
-      </c>
-      <c r="F52" t="n">
-        <v>924.86</v>
-      </c>
-      <c r="G52" t="n">
-        <v>915.78</v>
-      </c>
-      <c r="H52" t="n">
-        <v>911.16</v>
-      </c>
-      <c r="I52" t="n">
-        <v>915.34</v>
-      </c>
       <c r="J52" t="n">
-        <v>900.34</v>
+        <v>916.6799999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>923.7</v>
+        <v>911.4400000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>914.4680000000001</v>
+        <v>915.2159999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>10.64493107795715</v>
+        <v>7.90850830078125</v>
       </c>
       <c r="C2" t="n">
-        <v>9.554492950439453</v>
+        <v>8.704927444458008</v>
       </c>
       <c r="D2" t="n">
-        <v>10.36783218383789</v>
+        <v>11.00649857521057</v>
       </c>
       <c r="E2" t="n">
-        <v>7.296191215515137</v>
+        <v>8.325710296630859</v>
       </c>
       <c r="F2" t="n">
-        <v>7.869549036026001</v>
+        <v>8.359169244766235</v>
       </c>
       <c r="G2" t="n">
-        <v>8.743803024291992</v>
+        <v>8.817980766296387</v>
       </c>
       <c r="H2" t="n">
-        <v>8.785809755325317</v>
+        <v>7.899659872055054</v>
       </c>
       <c r="I2" t="n">
-        <v>7.335851192474365</v>
+        <v>7.974981307983398</v>
       </c>
       <c r="J2" t="n">
-        <v>9.286241292953491</v>
+        <v>8.961058855056763</v>
       </c>
       <c r="K2" t="n">
-        <v>8.506420850753784</v>
+        <v>8.983284950256348</v>
       </c>
       <c r="L2" t="n">
-        <v>8.839112257957458</v>
+        <v>8.694177961349487</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>8.939031362533569</v>
+        <v>9.81599497795105</v>
       </c>
       <c r="C3" t="n">
-        <v>7.932880163192749</v>
+        <v>11.14064788818359</v>
       </c>
       <c r="D3" t="n">
-        <v>8.298922061920166</v>
+        <v>9.497820138931274</v>
       </c>
       <c r="E3" t="n">
-        <v>7.418724536895752</v>
+        <v>9.09593653678894</v>
       </c>
       <c r="F3" t="n">
-        <v>7.549445390701294</v>
+        <v>7.802579402923584</v>
       </c>
       <c r="G3" t="n">
-        <v>8.616577863693237</v>
+        <v>8.395908355712891</v>
       </c>
       <c r="H3" t="n">
-        <v>9.523737668991089</v>
+        <v>9.907657861709595</v>
       </c>
       <c r="I3" t="n">
-        <v>7.409737110137939</v>
+        <v>7.987188339233398</v>
       </c>
       <c r="J3" t="n">
-        <v>7.50110912322998</v>
+        <v>9.569743871688843</v>
       </c>
       <c r="K3" t="n">
-        <v>7.913345575332642</v>
+        <v>9.84254002571106</v>
       </c>
       <c r="L3" t="n">
-        <v>8.110351085662842</v>
+        <v>9.305601739883423</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>7.696904182434082</v>
+        <v>9.361681938171387</v>
       </c>
       <c r="C4" t="n">
-        <v>9.055952548980713</v>
+        <v>8.402645349502563</v>
       </c>
       <c r="D4" t="n">
-        <v>7.581324577331543</v>
+        <v>8.669239521026611</v>
       </c>
       <c r="E4" t="n">
-        <v>9.063431024551392</v>
+        <v>8.043617725372314</v>
       </c>
       <c r="F4" t="n">
-        <v>6.888583183288574</v>
+        <v>7.851793050765991</v>
       </c>
       <c r="G4" t="n">
-        <v>7.18828821182251</v>
+        <v>8.09070611000061</v>
       </c>
       <c r="H4" t="n">
-        <v>7.599247217178345</v>
+        <v>8.053511142730713</v>
       </c>
       <c r="I4" t="n">
-        <v>7.326440334320068</v>
+        <v>8.944671154022217</v>
       </c>
       <c r="J4" t="n">
-        <v>8.018166542053223</v>
+        <v>8.181880235671997</v>
       </c>
       <c r="K4" t="n">
-        <v>6.886078357696533</v>
+        <v>8.209399700164795</v>
       </c>
       <c r="L4" t="n">
-        <v>7.730441617965698</v>
+        <v>8.38091459274292</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>6.917518377304077</v>
+        <v>8.447891235351562</v>
       </c>
       <c r="C5" t="n">
-        <v>6.878585338592529</v>
+        <v>7.696499109268188</v>
       </c>
       <c r="D5" t="n">
-        <v>6.715030193328857</v>
+        <v>7.346662521362305</v>
       </c>
       <c r="E5" t="n">
-        <v>7.18834114074707</v>
+        <v>8.783175230026245</v>
       </c>
       <c r="F5" t="n">
-        <v>7.061655044555664</v>
+        <v>8.439139604568481</v>
       </c>
       <c r="G5" t="n">
-        <v>7.903099060058594</v>
+        <v>8.16539740562439</v>
       </c>
       <c r="H5" t="n">
-        <v>8.000609874725342</v>
+        <v>8.056671142578125</v>
       </c>
       <c r="I5" t="n">
-        <v>6.653055191040039</v>
+        <v>9.206612348556519</v>
       </c>
       <c r="J5" t="n">
-        <v>6.89891791343689</v>
+        <v>8.085391044616699</v>
       </c>
       <c r="K5" t="n">
-        <v>6.841558694839478</v>
+        <v>7.74263596534729</v>
       </c>
       <c r="L5" t="n">
-        <v>7.105837082862854</v>
+        <v>8.197007560729981</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>6.430098295211792</v>
+        <v>8.299262523651123</v>
       </c>
       <c r="C6" t="n">
-        <v>6.850568771362305</v>
+        <v>8.450533390045166</v>
       </c>
       <c r="D6" t="n">
-        <v>6.976238012313843</v>
+        <v>8.392188549041748</v>
       </c>
       <c r="E6" t="n">
-        <v>9.361649751663208</v>
+        <v>8.767459154129028</v>
       </c>
       <c r="F6" t="n">
-        <v>6.67601490020752</v>
+        <v>7.796578645706177</v>
       </c>
       <c r="G6" t="n">
-        <v>7.339322805404663</v>
+        <v>8.344121932983398</v>
       </c>
       <c r="H6" t="n">
-        <v>8.608086109161377</v>
+        <v>7.834530830383301</v>
       </c>
       <c r="I6" t="n">
-        <v>7.537333250045776</v>
+        <v>7.953708171844482</v>
       </c>
       <c r="J6" t="n">
-        <v>7.882955074310303</v>
+        <v>8.360039472579956</v>
       </c>
       <c r="K6" t="n">
-        <v>8.794660329818726</v>
+        <v>7.56347131729126</v>
       </c>
       <c r="L6" t="n">
-        <v>7.645692729949952</v>
+        <v>8.176189398765564</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>7.931343793869019</v>
+        <v>8.692171096801758</v>
       </c>
       <c r="C7" t="n">
-        <v>7.106441736221313</v>
+        <v>8.381526947021484</v>
       </c>
       <c r="D7" t="n">
-        <v>7.277976751327515</v>
+        <v>7.946874856948853</v>
       </c>
       <c r="E7" t="n">
-        <v>7.737783908843994</v>
+        <v>9.073883056640625</v>
       </c>
       <c r="F7" t="n">
-        <v>8.222094058990479</v>
+        <v>10.04786252975464</v>
       </c>
       <c r="G7" t="n">
-        <v>9.126225233078003</v>
+        <v>8.126974582672119</v>
       </c>
       <c r="H7" t="n">
-        <v>7.467492818832397</v>
+        <v>8.138901233673096</v>
       </c>
       <c r="I7" t="n">
-        <v>7.638527870178223</v>
+        <v>7.929174661636353</v>
       </c>
       <c r="J7" t="n">
-        <v>7.821090221405029</v>
+        <v>8.473824977874756</v>
       </c>
       <c r="K7" t="n">
-        <v>7.329816818237305</v>
+        <v>8.062175035476685</v>
       </c>
       <c r="L7" t="n">
-        <v>7.765879321098327</v>
+        <v>8.487336897850037</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>7.964723348617554</v>
+        <v>8.238521099090576</v>
       </c>
       <c r="C8" t="n">
-        <v>7.451000928878784</v>
+        <v>9.052113056182861</v>
       </c>
       <c r="D8" t="n">
-        <v>7.402171850204468</v>
+        <v>9.203944206237793</v>
       </c>
       <c r="E8" t="n">
-        <v>7.461989641189575</v>
+        <v>7.803403854370117</v>
       </c>
       <c r="F8" t="n">
-        <v>7.601648569107056</v>
+        <v>8.935375690460205</v>
       </c>
       <c r="G8" t="n">
-        <v>7.08746862411499</v>
+        <v>9.11518669128418</v>
       </c>
       <c r="H8" t="n">
-        <v>8.151748657226562</v>
+        <v>8.473585367202759</v>
       </c>
       <c r="I8" t="n">
-        <v>7.944270372390747</v>
+        <v>8.949756622314453</v>
       </c>
       <c r="J8" t="n">
-        <v>7.174714088439941</v>
+        <v>8.3349609375</v>
       </c>
       <c r="K8" t="n">
-        <v>7.552794933319092</v>
+        <v>8.266845941543579</v>
       </c>
       <c r="L8" t="n">
-        <v>7.579253101348877</v>
+        <v>8.637369346618652</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>7.967358112335205</v>
+        <v>10.13804340362549</v>
       </c>
       <c r="C9" t="n">
-        <v>7.000167846679688</v>
+        <v>8.161876201629639</v>
       </c>
       <c r="D9" t="n">
-        <v>8.554226875305176</v>
+        <v>8.405789136886597</v>
       </c>
       <c r="E9" t="n">
-        <v>7.313292980194092</v>
+        <v>9.790809154510498</v>
       </c>
       <c r="F9" t="n">
-        <v>7.365741491317749</v>
+        <v>11.73654556274414</v>
       </c>
       <c r="G9" t="n">
-        <v>7.559258460998535</v>
+        <v>8.567774295806885</v>
       </c>
       <c r="H9" t="n">
-        <v>8.006633043289185</v>
+        <v>10.05401873588562</v>
       </c>
       <c r="I9" t="n">
-        <v>7.943568706512451</v>
+        <v>8.050909519195557</v>
       </c>
       <c r="J9" t="n">
-        <v>7.730478763580322</v>
+        <v>8.472824096679688</v>
       </c>
       <c r="K9" t="n">
-        <v>7.440658569335938</v>
+        <v>7.787185907363892</v>
       </c>
       <c r="L9" t="n">
-        <v>7.688138484954834</v>
+        <v>9.1165776014328</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>6.934441089630127</v>
+        <v>7.627477407455444</v>
       </c>
       <c r="C10" t="n">
-        <v>6.708287239074707</v>
+        <v>7.659140586853027</v>
       </c>
       <c r="D10" t="n">
-        <v>7.008640289306641</v>
+        <v>7.621528148651123</v>
       </c>
       <c r="E10" t="n">
-        <v>6.654909372329712</v>
+        <v>8.521019697189331</v>
       </c>
       <c r="F10" t="n">
-        <v>6.956410884857178</v>
+        <v>7.324634313583374</v>
       </c>
       <c r="G10" t="n">
-        <v>6.51056170463562</v>
+        <v>6.986263513565063</v>
       </c>
       <c r="H10" t="n">
-        <v>6.647704362869263</v>
+        <v>7.650023937225342</v>
       </c>
       <c r="I10" t="n">
-        <v>7.752841949462891</v>
+        <v>7.248605489730835</v>
       </c>
       <c r="J10" t="n">
-        <v>6.448216438293457</v>
+        <v>7.723476648330688</v>
       </c>
       <c r="K10" t="n">
-        <v>6.850998878479004</v>
+        <v>7.646230936050415</v>
       </c>
       <c r="L10" t="n">
-        <v>6.84730122089386</v>
+        <v>7.600840067863464</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>6.549866914749146</v>
+        <v>8.193645238876343</v>
       </c>
       <c r="C11" t="n">
-        <v>7.326703786849976</v>
+        <v>8.83983302116394</v>
       </c>
       <c r="D11" t="n">
-        <v>7.24820613861084</v>
+        <v>8.05506443977356</v>
       </c>
       <c r="E11" t="n">
-        <v>7.756878137588501</v>
+        <v>7.768344163894653</v>
       </c>
       <c r="F11" t="n">
-        <v>7.156939268112183</v>
+        <v>8.725723505020142</v>
       </c>
       <c r="G11" t="n">
-        <v>7.186405897140503</v>
+        <v>7.846032619476318</v>
       </c>
       <c r="H11" t="n">
-        <v>7.137005090713501</v>
+        <v>8.425291538238525</v>
       </c>
       <c r="I11" t="n">
-        <v>6.913572311401367</v>
+        <v>7.18194055557251</v>
       </c>
       <c r="J11" t="n">
-        <v>8.458147764205933</v>
+        <v>7.482467412948608</v>
       </c>
       <c r="K11" t="n">
-        <v>6.902569055557251</v>
+        <v>7.450037956237793</v>
       </c>
       <c r="L11" t="n">
-        <v>7.26362943649292</v>
+        <v>7.996838045120239</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>7.618177175521851</v>
+        <v>7.748989582061768</v>
       </c>
       <c r="C12" t="n">
-        <v>7.460062026977539</v>
+        <v>7.776761054992676</v>
       </c>
       <c r="D12" t="n">
-        <v>6.999806642532349</v>
+        <v>8.257086992263794</v>
       </c>
       <c r="E12" t="n">
-        <v>7.820036172866821</v>
+        <v>7.512501955032349</v>
       </c>
       <c r="F12" t="n">
-        <v>7.615872621536255</v>
+        <v>7.984767913818359</v>
       </c>
       <c r="G12" t="n">
-        <v>6.79583215713501</v>
+        <v>8.176743507385254</v>
       </c>
       <c r="H12" t="n">
-        <v>7.667542695999146</v>
+        <v>7.699129104614258</v>
       </c>
       <c r="I12" t="n">
-        <v>6.748835325241089</v>
+        <v>8.15735387802124</v>
       </c>
       <c r="J12" t="n">
-        <v>6.872489213943481</v>
+        <v>8.729235410690308</v>
       </c>
       <c r="K12" t="n">
-        <v>6.988229990005493</v>
+        <v>8.057776927947998</v>
       </c>
       <c r="L12" t="n">
-        <v>7.258688402175903</v>
+        <v>8.0100346326828</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>7.016125202178955</v>
+        <v>8.17403244972229</v>
       </c>
       <c r="C13" t="n">
-        <v>6.7463219165802</v>
+        <v>7.386066198348999</v>
       </c>
       <c r="D13" t="n">
-        <v>7.287930727005005</v>
+        <v>7.297857522964478</v>
       </c>
       <c r="E13" t="n">
-        <v>6.650071859359741</v>
+        <v>8.960161209106445</v>
       </c>
       <c r="F13" t="n">
-        <v>6.925888538360596</v>
+        <v>7.000900745391846</v>
       </c>
       <c r="G13" t="n">
-        <v>7.145808219909668</v>
+        <v>8.820703506469727</v>
       </c>
       <c r="H13" t="n">
-        <v>7.037691116333008</v>
+        <v>8.321754932403564</v>
       </c>
       <c r="I13" t="n">
-        <v>6.834600210189819</v>
+        <v>7.499952793121338</v>
       </c>
       <c r="J13" t="n">
-        <v>6.506289005279541</v>
+        <v>7.453756809234619</v>
       </c>
       <c r="K13" t="n">
-        <v>7.147967100143433</v>
+        <v>8.037712812423706</v>
       </c>
       <c r="L13" t="n">
-        <v>6.929869389533996</v>
+        <v>7.895289897918701</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>10.40278005599976</v>
+        <v>8.333164930343628</v>
       </c>
       <c r="C14" t="n">
-        <v>8.593905925750732</v>
+        <v>8.550684690475464</v>
       </c>
       <c r="D14" t="n">
-        <v>8.104901552200317</v>
+        <v>12.19882011413574</v>
       </c>
       <c r="E14" t="n">
-        <v>7.960758447647095</v>
+        <v>10.48512125015259</v>
       </c>
       <c r="F14" t="n">
-        <v>8.216452121734619</v>
+        <v>8.67938756942749</v>
       </c>
       <c r="G14" t="n">
-        <v>8.378270149230957</v>
+        <v>8.312847137451172</v>
       </c>
       <c r="H14" t="n">
-        <v>8.681971788406372</v>
+        <v>9.136700868606567</v>
       </c>
       <c r="I14" t="n">
-        <v>7.65347146987915</v>
+        <v>8.959739208221436</v>
       </c>
       <c r="J14" t="n">
-        <v>8.762216329574585</v>
+        <v>8.694379329681396</v>
       </c>
       <c r="K14" t="n">
-        <v>9.852530479431152</v>
+        <v>8.523337364196777</v>
       </c>
       <c r="L14" t="n">
-        <v>8.660725831985474</v>
+        <v>9.187418246269226</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>9.973097562789917</v>
+        <v>10.67918586730957</v>
       </c>
       <c r="C15" t="n">
-        <v>10.00538682937622</v>
+        <v>8.482447385787964</v>
       </c>
       <c r="D15" t="n">
-        <v>8.87449312210083</v>
+        <v>7.90292501449585</v>
       </c>
       <c r="E15" t="n">
-        <v>9.618021726608276</v>
+        <v>9.401554346084595</v>
       </c>
       <c r="F15" t="n">
-        <v>11.75788879394531</v>
+        <v>8.250510454177856</v>
       </c>
       <c r="G15" t="n">
-        <v>10.84571194648743</v>
+        <v>7.840131759643555</v>
       </c>
       <c r="H15" t="n">
-        <v>11.23389720916748</v>
+        <v>8.42762279510498</v>
       </c>
       <c r="I15" t="n">
-        <v>12.58385944366455</v>
+        <v>9.083340167999268</v>
       </c>
       <c r="J15" t="n">
-        <v>10.89987254142761</v>
+        <v>8.617004632949829</v>
       </c>
       <c r="K15" t="n">
-        <v>8.777810096740723</v>
+        <v>8.563742160797119</v>
       </c>
       <c r="L15" t="n">
-        <v>10.45700392723083</v>
+        <v>8.724846458435058</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>8.986273765563965</v>
+        <v>7.589215278625488</v>
       </c>
       <c r="C16" t="n">
-        <v>7.759824275970459</v>
+        <v>7.299871206283569</v>
       </c>
       <c r="D16" t="n">
-        <v>9.231607437133789</v>
+        <v>9.484293937683105</v>
       </c>
       <c r="E16" t="n">
-        <v>7.371325492858887</v>
+        <v>7.571216106414795</v>
       </c>
       <c r="F16" t="n">
-        <v>9.386881589889526</v>
+        <v>7.395148515701294</v>
       </c>
       <c r="G16" t="n">
-        <v>8.264547109603882</v>
+        <v>7.68489933013916</v>
       </c>
       <c r="H16" t="n">
-        <v>7.095963478088379</v>
+        <v>7.032061576843262</v>
       </c>
       <c r="I16" t="n">
-        <v>7.268037796020508</v>
+        <v>7.424116373062134</v>
       </c>
       <c r="J16" t="n">
-        <v>7.083478927612305</v>
+        <v>8.028837203979492</v>
       </c>
       <c r="K16" t="n">
-        <v>8.645111083984375</v>
+        <v>7.787723302841187</v>
       </c>
       <c r="L16" t="n">
-        <v>8.109305095672607</v>
+        <v>7.729738283157348</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>9.787115812301636</v>
+        <v>8.340816974639893</v>
       </c>
       <c r="C17" t="n">
-        <v>7.88382887840271</v>
+        <v>9.089932203292847</v>
       </c>
       <c r="D17" t="n">
-        <v>7.323458194732666</v>
+        <v>7.388270139694214</v>
       </c>
       <c r="E17" t="n">
-        <v>7.440153360366821</v>
+        <v>8.403112888336182</v>
       </c>
       <c r="F17" t="n">
-        <v>8.493589162826538</v>
+        <v>10.79889154434204</v>
       </c>
       <c r="G17" t="n">
-        <v>8.149804592132568</v>
+        <v>9.425444602966309</v>
       </c>
       <c r="H17" t="n">
-        <v>7.46959924697876</v>
+        <v>8.876405477523804</v>
       </c>
       <c r="I17" t="n">
-        <v>8.125425577163696</v>
+        <v>8.145291090011597</v>
       </c>
       <c r="J17" t="n">
-        <v>8.068152189254761</v>
+        <v>9.789775133132935</v>
       </c>
       <c r="K17" t="n">
-        <v>10.93368554115295</v>
+        <v>7.877910852432251</v>
       </c>
       <c r="L17" t="n">
-        <v>8.367481255531311</v>
+        <v>8.813585090637208</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>8.121815204620361</v>
+        <v>8.514795541763306</v>
       </c>
       <c r="C18" t="n">
-        <v>8.863414525985718</v>
+        <v>9.086341142654419</v>
       </c>
       <c r="D18" t="n">
-        <v>7.786169290542603</v>
+        <v>9.857867479324341</v>
       </c>
       <c r="E18" t="n">
-        <v>10.08730983734131</v>
+        <v>10.00651383399963</v>
       </c>
       <c r="F18" t="n">
-        <v>8.237596035003662</v>
+        <v>9.934189558029175</v>
       </c>
       <c r="G18" t="n">
-        <v>11.66829013824463</v>
+        <v>9.357154369354248</v>
       </c>
       <c r="H18" t="n">
-        <v>8.608087301254272</v>
+        <v>10.67667198181152</v>
       </c>
       <c r="I18" t="n">
-        <v>9.182111263275146</v>
+        <v>8.661446571350098</v>
       </c>
       <c r="J18" t="n">
-        <v>7.998608827590942</v>
+        <v>8.67491626739502</v>
       </c>
       <c r="K18" t="n">
-        <v>9.244457244873047</v>
+        <v>9.136703968048096</v>
       </c>
       <c r="L18" t="n">
-        <v>8.97978596687317</v>
+        <v>9.390660071372986</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>6.123971462249756</v>
+        <v>6.459666967391968</v>
       </c>
       <c r="C19" t="n">
-        <v>6.002716541290283</v>
+        <v>7.077583074569702</v>
       </c>
       <c r="D19" t="n">
-        <v>6.456027507781982</v>
+        <v>7.347878456115723</v>
       </c>
       <c r="E19" t="n">
-        <v>7.169237375259399</v>
+        <v>6.277641773223877</v>
       </c>
       <c r="F19" t="n">
-        <v>6.069059371948242</v>
+        <v>7.201288223266602</v>
       </c>
       <c r="G19" t="n">
-        <v>8.029572725296021</v>
+        <v>7.058688640594482</v>
       </c>
       <c r="H19" t="n">
-        <v>7.043069124221802</v>
+        <v>8.148755550384521</v>
       </c>
       <c r="I19" t="n">
-        <v>6.360837459564209</v>
+        <v>7.977760314941406</v>
       </c>
       <c r="J19" t="n">
-        <v>6.155821800231934</v>
+        <v>7.679424285888672</v>
       </c>
       <c r="K19" t="n">
-        <v>6.017723083496094</v>
+        <v>8.037503957748413</v>
       </c>
       <c r="L19" t="n">
-        <v>6.542803645133972</v>
+        <v>7.326619124412536</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>7.376201152801514</v>
+        <v>8.578601837158203</v>
       </c>
       <c r="C20" t="n">
-        <v>8.129808187484741</v>
+        <v>7.368919610977173</v>
       </c>
       <c r="D20" t="n">
-        <v>7.286964893341064</v>
+        <v>8.02811598777771</v>
       </c>
       <c r="E20" t="n">
-        <v>7.626803398132324</v>
+        <v>8.940280914306641</v>
       </c>
       <c r="F20" t="n">
-        <v>7.711504936218262</v>
+        <v>7.946788549423218</v>
       </c>
       <c r="G20" t="n">
-        <v>9.432567358016968</v>
+        <v>7.611197948455811</v>
       </c>
       <c r="H20" t="n">
-        <v>7.331490278244019</v>
+        <v>8.016152858734131</v>
       </c>
       <c r="I20" t="n">
-        <v>7.589345216751099</v>
+        <v>9.579206705093384</v>
       </c>
       <c r="J20" t="n">
-        <v>10.62245917320251</v>
+        <v>7.598641633987427</v>
       </c>
       <c r="K20" t="n">
-        <v>8.255081176757812</v>
+        <v>7.658463001251221</v>
       </c>
       <c r="L20" t="n">
-        <v>8.136222577095031</v>
+        <v>8.132636904716492</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>7.666030168533325</v>
+        <v>7.992629289627075</v>
       </c>
       <c r="C21" t="n">
-        <v>7.960267543792725</v>
+        <v>8.753229856491089</v>
       </c>
       <c r="D21" t="n">
-        <v>7.862493276596069</v>
+        <v>8.80962085723877</v>
       </c>
       <c r="E21" t="n">
-        <v>9.265512943267822</v>
+        <v>8.033524036407471</v>
       </c>
       <c r="F21" t="n">
-        <v>8.201710224151611</v>
+        <v>8.050006628036499</v>
       </c>
       <c r="G21" t="n">
-        <v>7.604767799377441</v>
+        <v>8.249993801116943</v>
       </c>
       <c r="H21" t="n">
-        <v>7.67393946647644</v>
+        <v>8.370156764984131</v>
       </c>
       <c r="I21" t="n">
-        <v>7.310519933700562</v>
+        <v>7.692878007888794</v>
       </c>
       <c r="J21" t="n">
-        <v>8.271506547927856</v>
+        <v>8.958673477172852</v>
       </c>
       <c r="K21" t="n">
-        <v>7.680544853210449</v>
+        <v>8.315305948257446</v>
       </c>
       <c r="L21" t="n">
-        <v>7.94972927570343</v>
+        <v>8.322601866722106</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>7.5558021068573</v>
+        <v>7.601650476455688</v>
       </c>
       <c r="C22" t="n">
-        <v>8.326377630233765</v>
+        <v>9.688774824142456</v>
       </c>
       <c r="D22" t="n">
-        <v>6.993236780166626</v>
+        <v>7.401715755462646</v>
       </c>
       <c r="E22" t="n">
-        <v>7.915373563766479</v>
+        <v>7.816648006439209</v>
       </c>
       <c r="F22" t="n">
-        <v>7.501918315887451</v>
+        <v>8.954200029373169</v>
       </c>
       <c r="G22" t="n">
-        <v>7.784219264984131</v>
+        <v>7.168920278549194</v>
       </c>
       <c r="H22" t="n">
-        <v>6.812698364257812</v>
+        <v>7.490996360778809</v>
       </c>
       <c r="I22" t="n">
-        <v>6.771820545196533</v>
+        <v>8.221576452255249</v>
       </c>
       <c r="J22" t="n">
-        <v>7.255534648895264</v>
+        <v>9.455399751663208</v>
       </c>
       <c r="K22" t="n">
-        <v>7.077497005462646</v>
+        <v>7.206238508224487</v>
       </c>
       <c r="L22" t="n">
-        <v>7.399447822570801</v>
+        <v>8.100612044334412</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>9.781390905380249</v>
+        <v>10.68469429016113</v>
       </c>
       <c r="C23" t="n">
-        <v>8.417601108551025</v>
+        <v>10.43285751342773</v>
       </c>
       <c r="D23" t="n">
-        <v>8.525322198867798</v>
+        <v>8.267466068267822</v>
       </c>
       <c r="E23" t="n">
-        <v>9.759756326675415</v>
+        <v>9.357635259628296</v>
       </c>
       <c r="F23" t="n">
-        <v>9.736487150192261</v>
+        <v>9.007084131240845</v>
       </c>
       <c r="G23" t="n">
-        <v>9.807148456573486</v>
+        <v>9.463891983032227</v>
       </c>
       <c r="H23" t="n">
-        <v>9.785711765289307</v>
+        <v>8.588103294372559</v>
       </c>
       <c r="I23" t="n">
-        <v>8.558284282684326</v>
+        <v>10.73013591766357</v>
       </c>
       <c r="J23" t="n">
-        <v>10.50543355941772</v>
+        <v>9.234464645385742</v>
       </c>
       <c r="K23" t="n">
-        <v>10.01955485343933</v>
+        <v>9.394059419631958</v>
       </c>
       <c r="L23" t="n">
-        <v>9.489669060707092</v>
+        <v>9.516039252281189</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>7.594221830368042</v>
+        <v>7.16551661491394</v>
       </c>
       <c r="C24" t="n">
-        <v>7.845605134963989</v>
+        <v>7.93091082572937</v>
       </c>
       <c r="D24" t="n">
-        <v>8.302359580993652</v>
+        <v>7.519972801208496</v>
       </c>
       <c r="E24" t="n">
-        <v>8.475487470626831</v>
+        <v>7.520953893661499</v>
       </c>
       <c r="F24" t="n">
-        <v>8.492287158966064</v>
+        <v>7.183789968490601</v>
       </c>
       <c r="G24" t="n">
-        <v>6.687140703201294</v>
+        <v>8.364245891571045</v>
       </c>
       <c r="H24" t="n">
-        <v>8.484986782073975</v>
+        <v>8.084961175918579</v>
       </c>
       <c r="I24" t="n">
-        <v>7.178354501724243</v>
+        <v>7.612182855606079</v>
       </c>
       <c r="J24" t="n">
-        <v>8.938822507858276</v>
+        <v>6.933966398239136</v>
       </c>
       <c r="K24" t="n">
-        <v>8.085995674133301</v>
+        <v>7.300977945327759</v>
       </c>
       <c r="L24" t="n">
-        <v>8.008526134490968</v>
+        <v>7.56174783706665</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>9.658484220504761</v>
+        <v>9.490632295608521</v>
       </c>
       <c r="C25" t="n">
-        <v>10.87789559364319</v>
+        <v>8.557177066802979</v>
       </c>
       <c r="D25" t="n">
-        <v>8.682908296585083</v>
+        <v>10.09127593040466</v>
       </c>
       <c r="E25" t="n">
-        <v>10.18210935592651</v>
+        <v>9.474374532699585</v>
       </c>
       <c r="F25" t="n">
-        <v>10.99585914611816</v>
+        <v>9.944136619567871</v>
       </c>
       <c r="G25" t="n">
-        <v>10.88095879554749</v>
+        <v>10.38954401016235</v>
       </c>
       <c r="H25" t="n">
-        <v>9.495346069335938</v>
+        <v>8.915790557861328</v>
       </c>
       <c r="I25" t="n">
-        <v>10.43289661407471</v>
+        <v>9.795542001724243</v>
       </c>
       <c r="J25" t="n">
-        <v>9.46497106552124</v>
+        <v>11.25360703468323</v>
       </c>
       <c r="K25" t="n">
-        <v>9.226483106613159</v>
+        <v>8.618566751480103</v>
       </c>
       <c r="L25" t="n">
-        <v>9.989791226387023</v>
+        <v>9.653064680099487</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>8.905796766281128</v>
+        <v>8.453004121780396</v>
       </c>
       <c r="C26" t="n">
-        <v>8.940775871276855</v>
+        <v>8.178712844848633</v>
       </c>
       <c r="D26" t="n">
-        <v>9.437025308609009</v>
+        <v>9.191574096679688</v>
       </c>
       <c r="E26" t="n">
-        <v>9.952774286270142</v>
+        <v>8.133842706680298</v>
       </c>
       <c r="F26" t="n">
-        <v>8.659121990203857</v>
+        <v>7.87052845954895</v>
       </c>
       <c r="G26" t="n">
-        <v>8.506981372833252</v>
+        <v>8.489465951919556</v>
       </c>
       <c r="H26" t="n">
-        <v>9.126188278198242</v>
+        <v>9.698261499404907</v>
       </c>
       <c r="I26" t="n">
-        <v>8.033143520355225</v>
+        <v>7.866531848907471</v>
       </c>
       <c r="J26" t="n">
-        <v>7.682516574859619</v>
+        <v>7.839601993560791</v>
       </c>
       <c r="K26" t="n">
-        <v>8.559241533279419</v>
+        <v>8.249037742614746</v>
       </c>
       <c r="L26" t="n">
-        <v>8.780356550216675</v>
+        <v>8.397056126594544</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>7.845133543014526</v>
+        <v>8.67048978805542</v>
       </c>
       <c r="C27" t="n">
-        <v>9.752132177352905</v>
+        <v>8.78046727180481</v>
       </c>
       <c r="D27" t="n">
-        <v>9.270254135131836</v>
+        <v>8.321306228637695</v>
       </c>
       <c r="E27" t="n">
-        <v>11.53578209877014</v>
+        <v>8.767151117324829</v>
       </c>
       <c r="F27" t="n">
-        <v>8.939738750457764</v>
+        <v>8.824091672897339</v>
       </c>
       <c r="G27" t="n">
-        <v>8.579232215881348</v>
+        <v>8.593520164489746</v>
       </c>
       <c r="H27" t="n">
-        <v>8.256731271743774</v>
+        <v>9.111490726470947</v>
       </c>
       <c r="I27" t="n">
-        <v>9.467368602752686</v>
+        <v>9.35363507270813</v>
       </c>
       <c r="J27" t="n">
-        <v>8.48029899597168</v>
+        <v>8.682365417480469</v>
       </c>
       <c r="K27" t="n">
-        <v>8.202294111251831</v>
+        <v>8.714295864105225</v>
       </c>
       <c r="L27" t="n">
-        <v>9.032896590232848</v>
+        <v>8.781881332397461</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>7.255272150039673</v>
+        <v>8.452464818954468</v>
       </c>
       <c r="C28" t="n">
-        <v>7.975681066513062</v>
+        <v>7.419075012207031</v>
       </c>
       <c r="D28" t="n">
-        <v>7.752813577651978</v>
+        <v>7.519361734390259</v>
       </c>
       <c r="E28" t="n">
-        <v>8.62598443031311</v>
+        <v>7.264987707138062</v>
       </c>
       <c r="F28" t="n">
-        <v>8.781801223754883</v>
+        <v>7.939282417297363</v>
       </c>
       <c r="G28" t="n">
-        <v>7.17632794380188</v>
+        <v>8.60594630241394</v>
       </c>
       <c r="H28" t="n">
-        <v>7.640201807022095</v>
+        <v>6.828227043151855</v>
       </c>
       <c r="I28" t="n">
-        <v>7.780025243759155</v>
+        <v>7.468057155609131</v>
       </c>
       <c r="J28" t="n">
-        <v>6.986242532730103</v>
+        <v>7.703444719314575</v>
       </c>
       <c r="K28" t="n">
-        <v>7.312399625778198</v>
+        <v>8.510813474655151</v>
       </c>
       <c r="L28" t="n">
-        <v>7.728674960136414</v>
+        <v>7.771166038513184</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>7.618212938308716</v>
+        <v>8.035063505172729</v>
       </c>
       <c r="C29" t="n">
-        <v>7.88187575340271</v>
+        <v>8.352758169174194</v>
       </c>
       <c r="D29" t="n">
-        <v>7.787111282348633</v>
+        <v>8.343770265579224</v>
       </c>
       <c r="E29" t="n">
-        <v>8.692559242248535</v>
+        <v>7.701445579528809</v>
       </c>
       <c r="F29" t="n">
-        <v>7.6447434425354</v>
+        <v>8.058496475219727</v>
       </c>
       <c r="G29" t="n">
-        <v>7.733831167221069</v>
+        <v>7.937829971313477</v>
       </c>
       <c r="H29" t="n">
-        <v>7.819132328033447</v>
+        <v>7.897171258926392</v>
       </c>
       <c r="I29" t="n">
-        <v>7.160823583602905</v>
+        <v>7.677422523498535</v>
       </c>
       <c r="J29" t="n">
-        <v>7.59122109413147</v>
+        <v>8.181611776351929</v>
       </c>
       <c r="K29" t="n">
-        <v>8.025655508041382</v>
+        <v>8.024144411087036</v>
       </c>
       <c r="L29" t="n">
-        <v>7.795516633987427</v>
+        <v>8.020971393585205</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>7.632585763931274</v>
+        <v>8.665980577468872</v>
       </c>
       <c r="C30" t="n">
-        <v>7.441145420074463</v>
+        <v>8.698368549346924</v>
       </c>
       <c r="D30" t="n">
-        <v>7.644801139831543</v>
+        <v>7.688504695892334</v>
       </c>
       <c r="E30" t="n">
-        <v>7.822111368179321</v>
+        <v>6.814190149307251</v>
       </c>
       <c r="F30" t="n">
-        <v>8.273900270462036</v>
+        <v>8.684361219406128</v>
       </c>
       <c r="G30" t="n">
-        <v>7.591705083847046</v>
+        <v>7.096406936645508</v>
       </c>
       <c r="H30" t="n">
-        <v>7.0862877368927</v>
+        <v>7.735805988311768</v>
       </c>
       <c r="I30" t="n">
-        <v>8.612751483917236</v>
+        <v>7.266499042510986</v>
       </c>
       <c r="J30" t="n">
-        <v>8.653029918670654</v>
+        <v>7.346275568008423</v>
       </c>
       <c r="K30" t="n">
-        <v>7.903931617736816</v>
+        <v>7.515342712402344</v>
       </c>
       <c r="L30" t="n">
-        <v>7.866224980354309</v>
+        <v>7.751173543930054</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>10.52859354019165</v>
+        <v>8.930727481842041</v>
       </c>
       <c r="C31" t="n">
-        <v>10.53283476829529</v>
+        <v>8.064422845840454</v>
       </c>
       <c r="D31" t="n">
-        <v>8.189257621765137</v>
+        <v>8.623025894165039</v>
       </c>
       <c r="E31" t="n">
-        <v>9.039143562316895</v>
+        <v>7.833038806915283</v>
       </c>
       <c r="F31" t="n">
-        <v>8.201894521713257</v>
+        <v>7.859497308731079</v>
       </c>
       <c r="G31" t="n">
-        <v>9.989244222640991</v>
+        <v>7.371717929840088</v>
       </c>
       <c r="H31" t="n">
-        <v>8.015363931655884</v>
+        <v>8.631054162979126</v>
       </c>
       <c r="I31" t="n">
-        <v>10.45452404022217</v>
+        <v>8.206089735031128</v>
       </c>
       <c r="J31" t="n">
-        <v>11.05147171020508</v>
+        <v>7.341289758682251</v>
       </c>
       <c r="K31" t="n">
-        <v>9.599776029586792</v>
+        <v>9.252440214157104</v>
       </c>
       <c r="L31" t="n">
-        <v>9.560210394859315</v>
+        <v>8.211330413818359</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>10.12531757354736</v>
+        <v>8.993114471435547</v>
       </c>
       <c r="C32" t="n">
-        <v>9.162235021591187</v>
+        <v>8.35620903968811</v>
       </c>
       <c r="D32" t="n">
-        <v>11.00504541397095</v>
+        <v>10.66137766838074</v>
       </c>
       <c r="E32" t="n">
-        <v>9.09546971321106</v>
+        <v>9.204019069671631</v>
       </c>
       <c r="F32" t="n">
-        <v>9.909315347671509</v>
+        <v>10.2524094581604</v>
       </c>
       <c r="G32" t="n">
-        <v>8.028612375259399</v>
+        <v>8.75118613243103</v>
       </c>
       <c r="H32" t="n">
-        <v>8.758637189865112</v>
+        <v>9.814992666244507</v>
       </c>
       <c r="I32" t="n">
-        <v>8.905962228775024</v>
+        <v>8.481891393661499</v>
       </c>
       <c r="J32" t="n">
-        <v>10.68633556365967</v>
+        <v>9.527245283126831</v>
       </c>
       <c r="K32" t="n">
-        <v>10.52485227584839</v>
+        <v>9.047198057174683</v>
       </c>
       <c r="L32" t="n">
-        <v>9.620178270339967</v>
+        <v>9.308964323997497</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>7.583575010299683</v>
+        <v>9.618725299835205</v>
       </c>
       <c r="C33" t="n">
-        <v>6.977079629898071</v>
+        <v>7.960766315460205</v>
       </c>
       <c r="D33" t="n">
-        <v>6.77081823348999</v>
+        <v>7.656502246856689</v>
       </c>
       <c r="E33" t="n">
-        <v>8.258064031600952</v>
+        <v>7.939297914505005</v>
       </c>
       <c r="F33" t="n">
-        <v>8.436775684356689</v>
+        <v>7.955211877822876</v>
       </c>
       <c r="G33" t="n">
-        <v>9.423559904098511</v>
+        <v>9.12375545501709</v>
       </c>
       <c r="H33" t="n">
-        <v>8.366203546524048</v>
+        <v>7.61108660697937</v>
       </c>
       <c r="I33" t="n">
-        <v>8.374913454055786</v>
+        <v>7.485451936721802</v>
       </c>
       <c r="J33" t="n">
-        <v>7.82316780090332</v>
+        <v>7.341774702072144</v>
       </c>
       <c r="K33" t="n">
-        <v>8.42865514755249</v>
+        <v>9.702784776687622</v>
       </c>
       <c r="L33" t="n">
-        <v>8.044281244277954</v>
+        <v>8.239535713195801</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>8.597182273864746</v>
+        <v>8.230015516281128</v>
       </c>
       <c r="C34" t="n">
-        <v>7.817861318588257</v>
+        <v>8.067964315414429</v>
       </c>
       <c r="D34" t="n">
-        <v>8.337738990783691</v>
+        <v>8.952701807022095</v>
       </c>
       <c r="E34" t="n">
-        <v>7.96629786491394</v>
+        <v>9.309843778610229</v>
       </c>
       <c r="F34" t="n">
-        <v>9.083034992218018</v>
+        <v>8.085898637771606</v>
       </c>
       <c r="G34" t="n">
-        <v>7.874517679214478</v>
+        <v>8.090899467468262</v>
       </c>
       <c r="H34" t="n">
-        <v>7.352583885192871</v>
+        <v>8.53876805305481</v>
       </c>
       <c r="I34" t="n">
-        <v>8.435961008071899</v>
+        <v>7.890882968902588</v>
       </c>
       <c r="J34" t="n">
-        <v>7.788262844085693</v>
+        <v>8.672399520874023</v>
       </c>
       <c r="K34" t="n">
-        <v>9.129364252090454</v>
+        <v>9.586580514907837</v>
       </c>
       <c r="L34" t="n">
-        <v>8.238280510902404</v>
+        <v>8.5425954580307</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>7.413564920425415</v>
+        <v>8.857497930526733</v>
       </c>
       <c r="C35" t="n">
-        <v>8.387814283370972</v>
+        <v>8.244009017944336</v>
       </c>
       <c r="D35" t="n">
-        <v>9.875522613525391</v>
+        <v>7.709842681884766</v>
       </c>
       <c r="E35" t="n">
-        <v>8.847571134567261</v>
+        <v>7.596658945083618</v>
       </c>
       <c r="F35" t="n">
-        <v>9.200968027114868</v>
+        <v>7.58666205406189</v>
       </c>
       <c r="G35" t="n">
-        <v>11.18834042549133</v>
+        <v>8.26694655418396</v>
       </c>
       <c r="H35" t="n">
-        <v>9.148885011672974</v>
+        <v>8.30533504486084</v>
       </c>
       <c r="I35" t="n">
-        <v>7.835091114044189</v>
+        <v>7.666910171508789</v>
       </c>
       <c r="J35" t="n">
-        <v>7.924344062805176</v>
+        <v>7.832662582397461</v>
       </c>
       <c r="K35" t="n">
-        <v>8.060511350631714</v>
+        <v>8.209625720977783</v>
       </c>
       <c r="L35" t="n">
-        <v>8.788261294364929</v>
+        <v>8.027615070343018</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>8.619009494781494</v>
+        <v>7.716551065444946</v>
       </c>
       <c r="C36" t="n">
-        <v>10.772864818573</v>
+        <v>7.95522141456604</v>
       </c>
       <c r="D36" t="n">
-        <v>8.020189046859741</v>
+        <v>8.732221126556396</v>
       </c>
       <c r="E36" t="n">
-        <v>8.708731651306152</v>
+        <v>8.022556781768799</v>
       </c>
       <c r="F36" t="n">
-        <v>8.150055646896362</v>
+        <v>8.595098257064819</v>
       </c>
       <c r="G36" t="n">
-        <v>10.57905507087708</v>
+        <v>7.896488666534424</v>
       </c>
       <c r="H36" t="n">
-        <v>9.716855525970459</v>
+        <v>8.076898336410522</v>
       </c>
       <c r="I36" t="n">
-        <v>11.45944976806641</v>
+        <v>7.912809133529663</v>
       </c>
       <c r="J36" t="n">
-        <v>9.240525722503662</v>
+        <v>7.833583831787109</v>
       </c>
       <c r="K36" t="n">
-        <v>8.124847173690796</v>
+        <v>7.50121808052063</v>
       </c>
       <c r="L36" t="n">
-        <v>9.339158391952514</v>
+        <v>8.024264669418335</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>7.547301292419434</v>
+        <v>7.592128753662109</v>
       </c>
       <c r="C37" t="n">
-        <v>7.305187225341797</v>
+        <v>7.369265556335449</v>
       </c>
       <c r="D37" t="n">
-        <v>8.232630729675293</v>
+        <v>7.48741602897644</v>
       </c>
       <c r="E37" t="n">
-        <v>7.48651385307312</v>
+        <v>7.117345333099365</v>
       </c>
       <c r="F37" t="n">
-        <v>8.432580947875977</v>
+        <v>7.085948467254639</v>
       </c>
       <c r="G37" t="n">
-        <v>7.648527383804321</v>
+        <v>8.012603044509888</v>
       </c>
       <c r="H37" t="n">
-        <v>8.018594741821289</v>
+        <v>7.596700429916382</v>
       </c>
       <c r="I37" t="n">
-        <v>8.810577869415283</v>
+        <v>7.876440048217773</v>
       </c>
       <c r="J37" t="n">
-        <v>8.300363540649414</v>
+        <v>8.340469598770142</v>
       </c>
       <c r="K37" t="n">
-        <v>7.529322147369385</v>
+        <v>8.235591411590576</v>
       </c>
       <c r="L37" t="n">
-        <v>7.931159973144531</v>
+        <v>7.671390867233276</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>7.759710073471069</v>
+        <v>7.164857864379883</v>
       </c>
       <c r="C38" t="n">
-        <v>7.894410371780396</v>
+        <v>7.628129959106445</v>
       </c>
       <c r="D38" t="n">
-        <v>7.66698169708252</v>
+        <v>7.26463508605957</v>
       </c>
       <c r="E38" t="n">
-        <v>8.193643093109131</v>
+        <v>7.934886455535889</v>
       </c>
       <c r="F38" t="n">
-        <v>7.590649604797363</v>
+        <v>8.737966060638428</v>
       </c>
       <c r="G38" t="n">
-        <v>7.544276237487793</v>
+        <v>7.670957326889038</v>
       </c>
       <c r="H38" t="n">
-        <v>8.269428730010986</v>
+        <v>7.181180238723755</v>
       </c>
       <c r="I38" t="n">
-        <v>8.704351663589478</v>
+        <v>7.607633352279663</v>
       </c>
       <c r="J38" t="n">
-        <v>7.95823335647583</v>
+        <v>7.495399713516235</v>
       </c>
       <c r="K38" t="n">
-        <v>7.781193971633911</v>
+        <v>7.504362344741821</v>
       </c>
       <c r="L38" t="n">
-        <v>7.936287879943848</v>
+        <v>7.619000840187073</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>8.727288484573364</v>
+        <v>10.07783126831055</v>
       </c>
       <c r="C39" t="n">
-        <v>8.45146918296814</v>
+        <v>9.027968168258667</v>
       </c>
       <c r="D39" t="n">
-        <v>8.566176652908325</v>
+        <v>9.801549673080444</v>
       </c>
       <c r="E39" t="n">
-        <v>8.445587396621704</v>
+        <v>7.931260347366333</v>
       </c>
       <c r="F39" t="n">
-        <v>9.44704794883728</v>
+        <v>8.547730922698975</v>
       </c>
       <c r="G39" t="n">
-        <v>10.51743841171265</v>
+        <v>8.805536270141602</v>
       </c>
       <c r="H39" t="n">
-        <v>11.35318827629089</v>
+        <v>8.107822895050049</v>
       </c>
       <c r="I39" t="n">
-        <v>9.250485420227051</v>
+        <v>8.711290121078491</v>
       </c>
       <c r="J39" t="n">
-        <v>8.66646409034729</v>
+        <v>8.035479545593262</v>
       </c>
       <c r="K39" t="n">
-        <v>8.441525220870972</v>
+        <v>9.303384304046631</v>
       </c>
       <c r="L39" t="n">
-        <v>9.186667108535767</v>
+        <v>8.8349853515625</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>7.908349990844727</v>
+        <v>7.448012351989746</v>
       </c>
       <c r="C40" t="n">
-        <v>8.245616912841797</v>
+        <v>7.458496809005737</v>
       </c>
       <c r="D40" t="n">
-        <v>8.603181600570679</v>
+        <v>7.467964887619019</v>
       </c>
       <c r="E40" t="n">
-        <v>8.70795464515686</v>
+        <v>7.440170764923096</v>
       </c>
       <c r="F40" t="n">
-        <v>9.593170404434204</v>
+        <v>9.055252313613892</v>
       </c>
       <c r="G40" t="n">
-        <v>8.726895809173584</v>
+        <v>8.43704628944397</v>
       </c>
       <c r="H40" t="n">
-        <v>8.23068642616272</v>
+        <v>8.100271224975586</v>
       </c>
       <c r="I40" t="n">
-        <v>8.488567113876343</v>
+        <v>8.107845067977905</v>
       </c>
       <c r="J40" t="n">
-        <v>9.141793489456177</v>
+        <v>7.787217855453491</v>
       </c>
       <c r="K40" t="n">
-        <v>7.969829797744751</v>
+        <v>7.263471126556396</v>
       </c>
       <c r="L40" t="n">
-        <v>8.561604619026184</v>
+        <v>7.856574869155883</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>8.757838487625122</v>
+        <v>7.14927077293396</v>
       </c>
       <c r="C41" t="n">
-        <v>8.525391101837158</v>
+        <v>7.818646669387817</v>
       </c>
       <c r="D41" t="n">
-        <v>8.848599910736084</v>
+        <v>7.449608564376831</v>
       </c>
       <c r="E41" t="n">
-        <v>8.341916561126709</v>
+        <v>7.392744779586792</v>
       </c>
       <c r="F41" t="n">
-        <v>7.783366441726685</v>
+        <v>8.004169225692749</v>
       </c>
       <c r="G41" t="n">
-        <v>8.431632041931152</v>
+        <v>7.181828498840332</v>
       </c>
       <c r="H41" t="n">
-        <v>8.479030132293701</v>
+        <v>7.624677658081055</v>
       </c>
       <c r="I41" t="n">
-        <v>8.765401124954224</v>
+        <v>8.106875419616699</v>
       </c>
       <c r="J41" t="n">
-        <v>8.134887456893921</v>
+        <v>7.583249807357788</v>
       </c>
       <c r="K41" t="n">
-        <v>8.292993307113647</v>
+        <v>7.484027147293091</v>
       </c>
       <c r="L41" t="n">
-        <v>8.436105656623841</v>
+        <v>7.579509854316711</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>8.513956308364868</v>
+        <v>9.586045265197754</v>
       </c>
       <c r="C42" t="n">
-        <v>8.737359762191772</v>
+        <v>7.606722831726074</v>
       </c>
       <c r="D42" t="n">
-        <v>11.27756237983704</v>
+        <v>7.406731843948364</v>
       </c>
       <c r="E42" t="n">
-        <v>8.911464929580688</v>
+        <v>8.113382816314697</v>
       </c>
       <c r="F42" t="n">
-        <v>8.767272710800171</v>
+        <v>7.659674644470215</v>
       </c>
       <c r="G42" t="n">
-        <v>8.638625621795654</v>
+        <v>9.071957111358643</v>
       </c>
       <c r="H42" t="n">
-        <v>8.710923433303833</v>
+        <v>7.605613231658936</v>
       </c>
       <c r="I42" t="n">
-        <v>8.596756935119629</v>
+        <v>8.837498664855957</v>
       </c>
       <c r="J42" t="n">
-        <v>8.955280780792236</v>
+        <v>7.618581771850586</v>
       </c>
       <c r="K42" t="n">
-        <v>8.482994318008423</v>
+        <v>7.671981811523438</v>
       </c>
       <c r="L42" t="n">
-        <v>8.959219717979432</v>
+        <v>8.117818999290467</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>9.709901571273804</v>
+        <v>7.407143115997314</v>
       </c>
       <c r="C43" t="n">
-        <v>8.477505207061768</v>
+        <v>9.272446870803833</v>
       </c>
       <c r="D43" t="n">
-        <v>9.160820007324219</v>
+        <v>7.852678060531616</v>
       </c>
       <c r="E43" t="n">
-        <v>9.287465810775757</v>
+        <v>7.730376482009888</v>
       </c>
       <c r="F43" t="n">
-        <v>9.14680552482605</v>
+        <v>7.907748222351074</v>
       </c>
       <c r="G43" t="n">
-        <v>9.099946975708008</v>
+        <v>6.988182067871094</v>
       </c>
       <c r="H43" t="n">
-        <v>8.985264778137207</v>
+        <v>7.4400475025177</v>
       </c>
       <c r="I43" t="n">
-        <v>8.962371587753296</v>
+        <v>8.552708148956299</v>
       </c>
       <c r="J43" t="n">
-        <v>9.135216474533081</v>
+        <v>8.58805251121521</v>
       </c>
       <c r="K43" t="n">
-        <v>8.513410806655884</v>
+        <v>7.39916467666626</v>
       </c>
       <c r="L43" t="n">
-        <v>9.047870874404907</v>
+        <v>7.913854765892029</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>8.068127632141113</v>
+        <v>6.690435886383057</v>
       </c>
       <c r="C44" t="n">
-        <v>7.64077615737915</v>
+        <v>6.777255058288574</v>
       </c>
       <c r="D44" t="n">
-        <v>8.541385412216187</v>
+        <v>6.746300220489502</v>
       </c>
       <c r="E44" t="n">
-        <v>7.848658084869385</v>
+        <v>9.282347202301025</v>
       </c>
       <c r="F44" t="n">
-        <v>7.886128425598145</v>
+        <v>6.729320287704468</v>
       </c>
       <c r="G44" t="n">
-        <v>7.530167818069458</v>
+        <v>6.799656629562378</v>
       </c>
       <c r="H44" t="n">
-        <v>7.252693176269531</v>
+        <v>6.867995023727417</v>
       </c>
       <c r="I44" t="n">
-        <v>8.421671867370605</v>
+        <v>7.008167505264282</v>
       </c>
       <c r="J44" t="n">
-        <v>7.72393798828125</v>
+        <v>7.584179639816284</v>
       </c>
       <c r="K44" t="n">
-        <v>8.255567789077759</v>
+        <v>6.72334361076355</v>
       </c>
       <c r="L44" t="n">
-        <v>7.916911435127258</v>
+        <v>7.120900106430054</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>9.708916425704956</v>
+        <v>10.88874626159668</v>
       </c>
       <c r="C45" t="n">
-        <v>10.50389361381531</v>
+        <v>9.009056329727173</v>
       </c>
       <c r="D45" t="n">
-        <v>10.58178853988647</v>
+        <v>10.35211801528931</v>
       </c>
       <c r="E45" t="n">
-        <v>10.91176795959473</v>
+        <v>8.808596134185791</v>
       </c>
       <c r="F45" t="n">
-        <v>10.03153038024902</v>
+        <v>8.846450805664062</v>
       </c>
       <c r="G45" t="n">
-        <v>10.62198495864868</v>
+        <v>10.79647827148438</v>
       </c>
       <c r="H45" t="n">
-        <v>9.168704509735107</v>
+        <v>9.255422592163086</v>
       </c>
       <c r="I45" t="n">
-        <v>9.059967041015625</v>
+        <v>10.6434051990509</v>
       </c>
       <c r="J45" t="n">
-        <v>9.489565372467041</v>
+        <v>10.42643857002258</v>
       </c>
       <c r="K45" t="n">
-        <v>11.9166088104248</v>
+        <v>8.783141851425171</v>
       </c>
       <c r="L45" t="n">
-        <v>10.19947276115417</v>
+        <v>9.780985403060914</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>8.294984340667725</v>
+        <v>8.673424005508423</v>
       </c>
       <c r="C46" t="n">
-        <v>9.877411603927612</v>
+        <v>7.721826791763306</v>
       </c>
       <c r="D46" t="n">
-        <v>7.929929971694946</v>
+        <v>7.003047227859497</v>
       </c>
       <c r="E46" t="n">
-        <v>8.139920473098755</v>
+        <v>7.693485260009766</v>
       </c>
       <c r="F46" t="n">
-        <v>7.850660562515259</v>
+        <v>7.709904193878174</v>
       </c>
       <c r="G46" t="n">
-        <v>8.354841709136963</v>
+        <v>8.529761075973511</v>
       </c>
       <c r="H46" t="n">
-        <v>8.388252258300781</v>
+        <v>7.834044694900513</v>
       </c>
       <c r="I46" t="n">
-        <v>10.25940251350403</v>
+        <v>8.980604410171509</v>
       </c>
       <c r="J46" t="n">
-        <v>8.248117208480835</v>
+        <v>7.987651109695435</v>
       </c>
       <c r="K46" t="n">
-        <v>8.092042684555054</v>
+        <v>8.685336351394653</v>
       </c>
       <c r="L46" t="n">
-        <v>8.543556332588196</v>
+        <v>8.081908512115479</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>9.29588770866394</v>
+        <v>8.883897304534912</v>
       </c>
       <c r="C47" t="n">
-        <v>10.96389317512512</v>
+        <v>9.264366149902344</v>
       </c>
       <c r="D47" t="n">
-        <v>9.091917037963867</v>
+        <v>9.056894540786743</v>
       </c>
       <c r="E47" t="n">
-        <v>9.838611602783203</v>
+        <v>10.43140268325806</v>
       </c>
       <c r="F47" t="n">
-        <v>11.12332653999329</v>
+        <v>8.287445545196533</v>
       </c>
       <c r="G47" t="n">
-        <v>10.10544991493225</v>
+        <v>8.804592609405518</v>
       </c>
       <c r="H47" t="n">
-        <v>10.20116281509399</v>
+        <v>8.66297459602356</v>
       </c>
       <c r="I47" t="n">
-        <v>10.28341031074524</v>
+        <v>8.269437074661255</v>
       </c>
       <c r="J47" t="n">
-        <v>9.596116065979004</v>
+        <v>8.916481971740723</v>
       </c>
       <c r="K47" t="n">
-        <v>10.84604382514954</v>
+        <v>9.871302127838135</v>
       </c>
       <c r="L47" t="n">
-        <v>10.13458189964294</v>
+        <v>9.044879460334778</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>7.746844053268433</v>
+        <v>7.158856391906738</v>
       </c>
       <c r="C48" t="n">
-        <v>7.546350955963135</v>
+        <v>7.958333015441895</v>
       </c>
       <c r="D48" t="n">
-        <v>7.743404388427734</v>
+        <v>6.518476009368896</v>
       </c>
       <c r="E48" t="n">
-        <v>8.512865304946899</v>
+        <v>7.175199270248413</v>
       </c>
       <c r="F48" t="n">
-        <v>7.269621133804321</v>
+        <v>7.368253707885742</v>
       </c>
       <c r="G48" t="n">
-        <v>7.11059832572937</v>
+        <v>7.23456335067749</v>
       </c>
       <c r="H48" t="n">
-        <v>7.292941808700562</v>
+        <v>6.467088460922241</v>
       </c>
       <c r="I48" t="n">
-        <v>7.030091285705566</v>
+        <v>7.331322431564331</v>
       </c>
       <c r="J48" t="n">
-        <v>7.412199974060059</v>
+        <v>7.755729913711548</v>
       </c>
       <c r="K48" t="n">
-        <v>6.955830812454224</v>
+        <v>6.694472551345825</v>
       </c>
       <c r="L48" t="n">
-        <v>7.46207480430603</v>
+        <v>7.166229510307312</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>8.886364221572876</v>
+        <v>8.021600246429443</v>
       </c>
       <c r="C49" t="n">
-        <v>8.424566268920898</v>
+        <v>7.517334699630737</v>
       </c>
       <c r="D49" t="n">
-        <v>7.854503154754639</v>
+        <v>8.102840423583984</v>
       </c>
       <c r="E49" t="n">
-        <v>7.72582745552063</v>
+        <v>7.071960926055908</v>
       </c>
       <c r="F49" t="n">
-        <v>7.685441732406616</v>
+        <v>8.107812643051147</v>
       </c>
       <c r="G49" t="n">
-        <v>8.158260345458984</v>
+        <v>7.110362529754639</v>
       </c>
       <c r="H49" t="n">
-        <v>9.344738006591797</v>
+        <v>7.346755027770996</v>
       </c>
       <c r="I49" t="n">
-        <v>8.400662660598755</v>
+        <v>7.465498924255371</v>
       </c>
       <c r="J49" t="n">
-        <v>7.881959915161133</v>
+        <v>7.367720127105713</v>
       </c>
       <c r="K49" t="n">
-        <v>8.424606800079346</v>
+        <v>7.838512659072876</v>
       </c>
       <c r="L49" t="n">
-        <v>8.278693056106567</v>
+        <v>7.595039820671081</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>9.888969659805298</v>
+        <v>7.748757839202881</v>
       </c>
       <c r="C50" t="n">
-        <v>8.420571327209473</v>
+        <v>8.166175603866577</v>
       </c>
       <c r="D50" t="n">
-        <v>10.0818727016449</v>
+        <v>11.10467267036438</v>
       </c>
       <c r="E50" t="n">
-        <v>8.089880228042603</v>
+        <v>8.0459885597229</v>
       </c>
       <c r="F50" t="n">
-        <v>7.970258712768555</v>
+        <v>9.309760093688965</v>
       </c>
       <c r="G50" t="n">
-        <v>9.712828636169434</v>
+        <v>8.88235878944397</v>
       </c>
       <c r="H50" t="n">
-        <v>7.804130792617798</v>
+        <v>9.418667078018188</v>
       </c>
       <c r="I50" t="n">
-        <v>8.314313888549805</v>
+        <v>8.794586896896362</v>
       </c>
       <c r="J50" t="n">
-        <v>7.921336650848389</v>
+        <v>8.452447414398193</v>
       </c>
       <c r="K50" t="n">
-        <v>9.91325044631958</v>
+        <v>7.858463287353516</v>
       </c>
       <c r="L50" t="n">
-        <v>8.811741304397582</v>
+        <v>8.778187823295593</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>7.54477858543396</v>
+        <v>8.093876600265503</v>
       </c>
       <c r="C51" t="n">
-        <v>6.946833848953247</v>
+        <v>7.557226657867432</v>
       </c>
       <c r="D51" t="n">
-        <v>8.494879245758057</v>
+        <v>7.931334495544434</v>
       </c>
       <c r="E51" t="n">
-        <v>8.402063846588135</v>
+        <v>7.414448022842407</v>
       </c>
       <c r="F51" t="n">
-        <v>9.030965805053711</v>
+        <v>7.716424942016602</v>
       </c>
       <c r="G51" t="n">
-        <v>6.680481195449829</v>
+        <v>7.278560638427734</v>
       </c>
       <c r="H51" t="n">
-        <v>7.452998399734497</v>
+        <v>7.251139640808105</v>
       </c>
       <c r="I51" t="n">
-        <v>7.063492774963379</v>
+        <v>7.201252460479736</v>
       </c>
       <c r="J51" t="n">
-        <v>7.182878732681274</v>
+        <v>7.628154277801514</v>
       </c>
       <c r="K51" t="n">
-        <v>7.376331329345703</v>
+        <v>8.291696786880493</v>
       </c>
       <c r="L51" t="n">
-        <v>7.617570376396179</v>
+        <v>7.636411452293396</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>8.32242331981659</v>
+        <v>8.425706162452698</v>
       </c>
       <c r="C52" t="n">
-        <v>8.28683268547058</v>
+        <v>8.284050512313843</v>
       </c>
       <c r="D52" t="n">
-        <v>8.278289184570312</v>
+        <v>8.418904666900636</v>
       </c>
       <c r="E52" t="n">
-        <v>8.43967559337616</v>
+        <v>8.278104529380798</v>
       </c>
       <c r="F52" t="n">
-        <v>8.351625075340271</v>
+        <v>8.362717838287354</v>
       </c>
       <c r="G52" t="n">
-        <v>8.485780262947083</v>
+        <v>8.244187221527099</v>
       </c>
       <c r="H52" t="n">
-        <v>8.291797561645508</v>
+        <v>8.225772132873535</v>
       </c>
       <c r="I52" t="n">
-        <v>8.27970272064209</v>
+        <v>8.234776344299316</v>
       </c>
       <c r="J52" t="n">
-        <v>8.285629229545593</v>
+        <v>8.292345170974732</v>
       </c>
       <c r="K52" t="n">
-        <v>8.3126930809021</v>
+        <v>8.199831285476684</v>
       </c>
       <c r="L52" t="n">
-        <v>8.333444871425629</v>
+        <v>8.296639586448668</v>
       </c>
     </row>
   </sheetData>
